--- a/monitor_targets.xlsx
+++ b/monitor_targets.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="93">
   <si>
     <t>기관명</t>
   </si>
@@ -25,84 +25,117 @@
     <t>게시판URL</t>
   </si>
   <si>
-    <t>우선순위</t>
-  </si>
-  <si>
-    <t>출처</t>
+    <t>경제인문사회연구회</t>
+  </si>
+  <si>
+    <t>서울요양원</t>
+  </si>
+  <si>
+    <t>재단법인 한국공공조직은행</t>
+  </si>
+  <si>
+    <t>한국건강가정진흥원</t>
+  </si>
+  <si>
+    <t>한국고전번역원</t>
+  </si>
+  <si>
+    <t>한국노인인력개발원</t>
+  </si>
+  <si>
+    <t>한국농수산식품유통공사</t>
+  </si>
+  <si>
+    <t>한국석유공사</t>
+  </si>
+  <si>
+    <t>한국세라믹기술원</t>
+  </si>
+  <si>
+    <t>한국주택금융공사</t>
+  </si>
+  <si>
+    <t>한국환경연구원</t>
   </si>
   <si>
     <t>강원대학교병원</t>
   </si>
   <si>
-    <t>경제인문사회연구회</t>
-  </si>
-  <si>
-    <t>서울요양원</t>
+    <t>국방기술품질원</t>
+  </si>
+  <si>
+    <t>대외경제정책연구원</t>
   </si>
   <si>
     <t>아시아·태평양경제협력체 기후센터</t>
   </si>
   <si>
-    <t>재단법인 한국공공조직은행</t>
-  </si>
-  <si>
-    <t>한국건강가정진흥원</t>
-  </si>
-  <si>
-    <t>한국고전번역원</t>
-  </si>
-  <si>
-    <t>한국노인인력개발원</t>
-  </si>
-  <si>
-    <t>한국농수산식품유통공사</t>
-  </si>
-  <si>
-    <t>한국석유공사</t>
-  </si>
-  <si>
-    <t>한국세라믹기술원</t>
-  </si>
-  <si>
     <t>한국원산지정보원</t>
   </si>
   <si>
-    <t>한국주택금융공사</t>
-  </si>
-  <si>
     <t>한국체육산업개발(주)</t>
   </si>
   <si>
     <t>한국해외인프라도시개발지원공사</t>
   </si>
   <si>
-    <t>한국환경연구원</t>
+    <t>공지사항 더보기</t>
   </si>
   <si>
     <t>공지사항</t>
   </si>
   <si>
+    <t>기관소식</t>
+  </si>
+  <si>
+    <t>알림마당</t>
+  </si>
+  <si>
+    <t>공지사항 더 보기 +</t>
+  </si>
+  <si>
     <t>연설문</t>
   </si>
   <si>
     <t>채용소식</t>
   </si>
   <si>
-    <t>공지사항 더보기</t>
+    <t>세미나/신청</t>
+  </si>
+  <si>
+    <t>KIEP 뉴스레터</t>
   </si>
   <si>
     <t>보도자료 더보기</t>
   </si>
   <si>
+    <t>요양원 소식</t>
+  </si>
+  <si>
+    <t>요양원소식 더보기</t>
+  </si>
+  <si>
     <t>연구보고서</t>
   </si>
   <si>
-    <t>기관소식</t>
+    <t>글로벌 기후소식</t>
   </si>
   <si>
     <t>국민토론방</t>
   </si>
   <si>
+    <t>번역원소식</t>
+  </si>
+  <si>
+    <t>전체</t>
+  </si>
+  <si>
+    <t>전자저널</t>
+  </si>
+  <si>
+    <t>고전번역연감</t>
+  </si>
+  <si>
     <t>개발원소식</t>
   </si>
   <si>
@@ -121,9 +154,6 @@
     <t>공모전</t>
   </si>
   <si>
-    <t>알림마당</t>
-  </si>
-  <si>
     <t>설문참여</t>
   </si>
   <si>
@@ -136,51 +166,108 @@
     <t>News Letter 뉴스레터 KEI 소식을 매달 종합하여 알려드립니다</t>
   </si>
   <si>
+    <t>https://www.nrc.re.kr/board.es?mid=a12101000000&amp;bid=0001</t>
+  </si>
+  <si>
+    <t>https://www.nrc.re.kr/menu.es?mid=a12101000000</t>
+  </si>
+  <si>
+    <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/Notice</t>
+  </si>
+  <si>
+    <t>https://kptb.kr/subpage_0501.asp</t>
+  </si>
+  <si>
+    <t>https://kptb.kr/subpage_0512.asp</t>
+  </si>
+  <si>
+    <t>https://www.kihf.or.kr/web/lay1/S1T1C838/sublink.do</t>
+  </si>
+  <si>
+    <t>https://www.kihf.or.kr/web/lay1/bbs/S1T838C97/A/3/list.do?rows=10&amp;cpage=1&amp;cat=&amp;article_seq=&amp;condition=TITLE&amp;keyword=</t>
+  </si>
+  <si>
+    <t>https://www.itkc.or.kr/bbs/board.do?id=2&amp;menuId=99</t>
+  </si>
+  <si>
+    <t>https://www.kordi.or.kr/content.do?cmsId=91</t>
+  </si>
+  <si>
+    <t>https://www.at.or.kr/article/apko364000/list.action</t>
+  </si>
+  <si>
+    <t>https://www.knoc.co.kr/sub05/sub05_5_5.jsp</t>
+  </si>
+  <si>
+    <t>https://www.kicet.re.kr/00117.web</t>
+  </si>
+  <si>
+    <t>https://www.kicet.re.kr/00120.web</t>
+  </si>
+  <si>
+    <t>https://www.kicet.re.kr/00020/00117/00120.web</t>
+  </si>
+  <si>
+    <t>https://www.hf.go.kr/ko/sub04/sub04_08.do</t>
+  </si>
+  <si>
+    <t>https://www.hf.go.kr/ko/sub05/sub08.do</t>
+  </si>
+  <si>
+    <t>https://www.kei.re.kr/menu.es?mid=a10301000000</t>
+  </si>
+  <si>
     <t>https://www.knuh.or.kr/hospitalinfo/hospitalinfo_03_01_list.asp</t>
   </si>
   <si>
-    <t>https://www.nrc.re.kr/menu.es?mid=a12101000000</t>
-  </si>
-  <si>
     <t>https://www.nrc.re.kr/menu.es?mid=a12001300000</t>
   </si>
   <si>
     <t>https://www.nrc.re.kr/menu.es?mid=a12105100000</t>
   </si>
   <si>
-    <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/Notice</t>
+    <t>https://www.dtaq.re.kr/ko/notice/seminar.jsp</t>
+  </si>
+  <si>
+    <t>https://www.kiep.go.kr/board.es?mid=a10508010000&amp;bid=0032&amp;cg_code=C01</t>
   </si>
   <si>
     <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/PressReleases</t>
   </si>
   <si>
+    <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews</t>
+  </si>
+  <si>
+    <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/News</t>
+  </si>
+  <si>
     <t>https://www.apcc21.org/board/BBSMSTR_000000000002?lang=ko</t>
   </si>
   <si>
-    <t>https://kptb.kr/subpage_0501.asp</t>
-  </si>
-  <si>
-    <t>https://kptb.kr/subpage_0512.asp</t>
-  </si>
-  <si>
-    <t>https://www.kihf.or.kr/web/lay1/bbs/S1T838C97/A/3/list.do?rows=10&amp;cpage=1&amp;cat=&amp;article_seq=&amp;condition=TITLE&amp;keyword=</t>
+    <t>https://www.apcc21.org/board/BBSMSTR_000000000065?lang=ko</t>
+  </si>
+  <si>
+    <t>https://www.apcc21.org/board/BBSMSTR_000000000065</t>
   </si>
   <si>
     <t>https://www.kihf.or.kr/web/lay1/program/S1T81C297/public/list.do?rows=10&amp;page_unit=0</t>
   </si>
   <si>
-    <t>https://www.itkc.or.kr/bbs/board.do?id=2&amp;menuId=99</t>
-  </si>
-  <si>
-    <t>https://www.kordi.or.kr/content.do?cmsId=91</t>
+    <t>https://www.itkc.or.kr/bbs/board.do?id=79&amp;menuId=100</t>
+  </si>
+  <si>
+    <t>https://www.itkc.or.kr/bbs/board.do?id=101&amp;menuId=10062</t>
+  </si>
+  <si>
+    <t>https://www.itkc.or.kr/bbs/board.do?id=74&amp;menuId=10161</t>
+  </si>
+  <si>
+    <t>https://www.itkc.or.kr/bbs/board.do?id=76&amp;menuId=86</t>
   </si>
   <si>
     <t>https://www.kordi.or.kr/content.do?cmsId=169</t>
   </si>
   <si>
-    <t>https://www.at.or.kr/article/apko364000/list.action</t>
-  </si>
-  <si>
     <t>https://www.at.or.kr/article/apko344800/list.action</t>
   </si>
   <si>
@@ -190,49 +277,22 @@
     <t>https://www.at.or.kr/article/apko318000/list.action</t>
   </si>
   <si>
-    <t>https://www.knoc.co.kr/sub05/sub05_5_5.jsp</t>
-  </si>
-  <si>
-    <t>https://www.kicet.re.kr/00020/00117/00120.web</t>
-  </si>
-  <si>
     <t>https://www.origin.or.kr/lay1/bbs/S1T11C34/F/26/list.do</t>
   </si>
   <si>
-    <t>https://www.hf.go.kr/ko/sub04/sub04_08.do</t>
-  </si>
-  <si>
     <t>https://www.hf.go.kr/ko/sub04/sub04_05_02.do</t>
   </si>
   <si>
-    <t>https://www.hf.go.kr/ko/sub05/sub08.do</t>
-  </si>
-  <si>
     <t>https://www.ksponco.or.kr/menu.es?mid=a10201020000</t>
   </si>
   <si>
     <t>https://www.kindkorea.or.kr/business/infra_office?board=17</t>
   </si>
   <si>
-    <t>https://www.kei.re.kr/menu.es?mid=a10301000000</t>
-  </si>
-  <si>
     <t>https://www.kei.re.kr/menu.es?mid=a10308040000</t>
   </si>
   <si>
     <t>https://www.kei.re.kr/menu.es?mid=a10308010000</t>
-  </si>
-  <si>
-    <t>V7.6 FINAL-보조</t>
-  </si>
-  <si>
-    <t>V7.6 KEEP-공지사항</t>
-  </si>
-  <si>
-    <t>V7.6 FINAL-공지사항</t>
-  </si>
-  <si>
-    <t>V7.6 ANALYZE-공지사항</t>
   </si>
 </sst>
 </file>
@@ -603,10 +663,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -616,501 +676,475 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" t="s">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" t="s">
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
+      <c r="C8" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-      <c r="E8" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>10</v>
       </c>
       <c r="B11" t="s">
         <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12">
-        <v>3</v>
-      </c>
-      <c r="E12" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-      <c r="E13" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
       <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>12</v>
       </c>
-      <c r="B15" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15">
-        <v>3</v>
-      </c>
-      <c r="E15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
-      </c>
       <c r="C17" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" t="s">
         <v>13</v>
       </c>
       <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>16</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18">
-        <v>3</v>
-      </c>
-      <c r="E18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" t="s">
+      <c r="C25" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>7</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>41</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" t="s">
+        <v>42</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>9</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>18</v>
+      </c>
+      <c r="B39" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>12</v>
+      </c>
+      <c r="B40" t="s">
+        <v>45</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>20</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
         <v>13</v>
       </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-      <c r="E22" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" t="s">
-        <v>35</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" t="s">
-        <v>18</v>
-      </c>
-      <c r="B26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" t="s">
-        <v>20</v>
-      </c>
-      <c r="B28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" t="s">
-        <v>20</v>
-      </c>
-      <c r="B29" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-      <c r="E29" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s">
-        <v>39</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-      <c r="E30" t="s">
-        <v>69</v>
+      <c r="B43" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>13</v>
+      </c>
+      <c r="B44" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -1144,6 +1178,20 @@
     <hyperlink ref="C28" r:id="rId27"/>
     <hyperlink ref="C29" r:id="rId28"/>
     <hyperlink ref="C30" r:id="rId29"/>
+    <hyperlink ref="C31" r:id="rId30"/>
+    <hyperlink ref="C32" r:id="rId31"/>
+    <hyperlink ref="C33" r:id="rId32"/>
+    <hyperlink ref="C34" r:id="rId33"/>
+    <hyperlink ref="C35" r:id="rId34"/>
+    <hyperlink ref="C36" r:id="rId35"/>
+    <hyperlink ref="C37" r:id="rId36"/>
+    <hyperlink ref="C38" r:id="rId37"/>
+    <hyperlink ref="C39" r:id="rId38"/>
+    <hyperlink ref="C40" r:id="rId39"/>
+    <hyperlink ref="C41" r:id="rId40"/>
+    <hyperlink ref="C42" r:id="rId41"/>
+    <hyperlink ref="C43" r:id="rId42"/>
+    <hyperlink ref="C44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/monitor_targets.xlsx
+++ b/monitor_targets.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="355기관" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'355기관'!$A$1:$E$356</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -16,28 +19,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="10"/>
-      <sz val="11"/>
-      <u val="single"/>
     </font>
   </fonts>
   <fills count="2">
@@ -48,7 +36,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -56,39 +44,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -451,3427 +415,8738 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D201"/>
+  <dimension ref="A1:E356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>기관명</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>URL</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>게시판명</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>홈페이지URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>공지게시판URL</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
         <is>
           <t>기관유형</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>URL상태</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>경제인문사회연구회</t>
+          <t>(사)남북교류협력지원협회</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://www.nrc.re.kr/menu.es?mid=a12101000000</t>
+          <t>https://www.sonosa.or.kr/</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://sonosa.or.kr/?menuno=12</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>경제인문사회연구회</t>
+          <t>(재)예술경영지원센터</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.nrc.re.kr/board.es?mid=a12101000000&amp;bid=0001</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>http://www.gokams.or.kr/</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>서울요양원</t>
+          <t>(재)우체국금융개발원</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/Notice</t>
+          <t>https://www.posid.or.kr/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.posid.or.kr/management/wishPr_list.do</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>재단법인 한국공공조직은행</t>
+          <t>(재)우체국물류지원단</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://kptb.kr/subpage_0501.asp</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.pola.or.kr/</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>한국건강가정진흥원</t>
+          <t>(재)우체국시설관리단</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.kihf.or.kr/web/lay1/bbs/S1T838C97/A/3/list.do?rows=10&amp;cpage=1&amp;cat=&amp;article_seq=&amp;condition=TITLE&amp;keyword=</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.poma.or.kr/</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>한국고전번역원</t>
+          <t>(재)일제강제동원피해자지원재단</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.itkc.or.kr/bbs/board.do?id=2&amp;menuId=99</t>
+          <t>https://www.fomo.or.kr/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.fomo.or.kr/kor/article/ATCL8a5c4c5fb/1221?mno=&amp;pageIndex=1&amp;searchCondition=&amp;searchKeyword=</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
+          <t>(재)축산환경관리원</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://www.kordi.or.kr/content.do?cmsId=91</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.lemi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>(재)한국보건의료정보원</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.at.or.kr/article/apko364000/list.action</t>
+          <t>https://www.khis.kr/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.khis.kr/menu.es?mid=a10301000000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>한국석유공사</t>
+          <t>(재)한국우편사업진흥원</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.knoc.co.kr/sub05/sub05_5_5.jsp</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.posa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>(재)한국통계정보원</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://www.kicet.re.kr/00020/00117/00120.web</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kosii.or.kr/</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>(재)한국통계진흥원</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.kicet.re.kr/00120.web</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>공지사항 더 보기 +</t>
+          <t>https://www.stat.or.kr/</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>한국수산자원공단</t>
+          <t>(주)강원랜드</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.fira.or.kr/newfira/web/news/news01_01.jsp</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://kangwonland.high1.com/</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>(주)공영홈쇼핑</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.hf.go.kr/ko/sub04/sub04_08.do</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.gongyoung.kr/</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>한국체육산업개발(주)</t>
+          <t>(주)한국가스기술공사</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.ksponco.or.kr/board.es?mid=a10301000000&amp;bid=0046</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kogas-tech.or.kr/</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>한국환경연구원</t>
+          <t>88관광개발(주)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.kei.re.kr/menu.es?mid=a10301000000</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.88countryclub.co.kr/</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>무역안보관리원</t>
+          <t>KDI국제정책대학원</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.kosti.or.kr/brd/board/212/L/menu/278?brdType=R&amp;bbsSn=11339</t>
+          <t>https://www.kdischool.ac.kr/</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Trade&amp;Security(개별본) [학술지 제10권-07] 미국 인공지능(AI) 인프라 정책과 시사점 - 트럼프 행정부 정책 변화를 중심으로_이주형</t>
+          <t>https://www.kdischool.ac.kr/news</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>아시아·태평양경제협력체 기후센터</t>
+          <t>가덕도신공항건설공단</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.apcc21.org/board/BBSMSTR_000000000016?lang=ko</t>
+          <t>https://www.g-airport.or.kr/</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>일반공지</t>
+          <t>https://www.g-airport.or.kr/kor/bbsctt/list.do?key=2409020035</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>한국건강가정진흥원</t>
+          <t>가축위생방역지원본부</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.kihf.or.kr/web/lay1/S1T1C838/sublink.do</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>https://www.lhca.or.kr/</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>한국세라믹기술원</t>
+          <t>강원대학교병원</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.kicet.re.kr/00117.web</t>
+          <t>https://www.knuh.or.kr/</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>알림마당</t>
+          <t>https://www.knuh.or.kr/hospitalinfo/hospitalinfo_03_01_list.asp</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>강원대학교치과병원</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.hf.go.kr/ko/sub05/sub08.do</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>http://www.knudh.or.kr/</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>재단법인 한국공공조직은행</t>
+          <t>건강보험심사평가원</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://kptb.kr/subpage_0512.asp</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>기관소식</t>
+          <t>https://www.hira.or.kr/</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>한국노인인력개발원</t>
+          <t>건설근로자공제회</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.kordi.or.kr/content.do?cmsId=169</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>개발원소식</t>
+          <t>https://www.cw.or.kr/</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>한국청소년정책연구원</t>
+          <t>건축공간연구원</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.nypi.re.kr/board?menuKey=D7eWzSzI7U&amp;siteId=SITE00002&amp;bbsId=BOARD00015</t>
+          <t>https://www.auri.re.kr/</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>기관소식</t>
+          <t>https://www.auri.re.kr/menu.es?mid=a10204060000</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>한국토지주택공사</t>
+          <t>게임물관리위원회</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.lh.or.kr/board.es?mid=a10601010000&amp;bid=0033</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>새소식</t>
+          <t>https://www.grac.or.kr/</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>경제인문사회연구회</t>
+          <t>경북대학교병원</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.nrc.re.kr/menu.es?mid=a12105100000</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>채용소식</t>
+          <t>http://knuh.kr/</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>서울요양원</t>
+          <t>경북대학교치과병원</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>요양원 소식</t>
+          <t>https://www.knudh.kr/</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>서울요양원</t>
+          <t>경상국립대학교병원</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/News</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>요양원소식 더보기</t>
+          <t>http://www.gnuh.co.kr/</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>아시아·태평양경제협력체 기후센터</t>
+          <t>경제인문사회연구회</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.apcc21.org/board/BBSMSTR_000000000065?lang=ko</t>
+          <t>https://www.nrc.re.kr/</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>글로벌 기후소식</t>
+          <t>https://www.nrc.re.kr/menu.es?mid=a12101000000</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>아시아·태평양경제협력체 기후센터</t>
+          <t>공간정보산업진흥원</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.apcc21.org/board/BBSMSTR_000000000065</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>글로벌 기후소식</t>
+          <t>https://www.spacen.or.kr/</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>한국고전번역원</t>
+          <t>공간정보품질관리원</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.itkc.or.kr/bbs/board.do?id=79&amp;menuId=100</t>
+          <t>https://www.siqms.or.kr/</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>번역원소식</t>
+          <t>https://www.siqms.or.kr/M2001000/board.do</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>한국원산지정보원</t>
+          <t>공무원연금공단</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.origin.or.kr/lay1/bbs/S1T11C34/F/26/list.do</t>
+          <t>https://www.geps.or.kr/</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FTA-PASS소식지</t>
+          <t>https://www.geps.or.kr/notiCommunication_info_incruit</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>한국환경연구원</t>
+          <t>과학기술사업화진흥원</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.kei.re.kr/menu.es?mid=a10308040000</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>KEI 소식지(OB-재직자)</t>
+          <t>https://www.compa.re.kr/</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>한국환경연구원</t>
+          <t>과학기술정책연구원</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.kei.re.kr/board.es?mid=a10308040000&amp;bid=0086</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>KEI 소식지(OB-재직자)</t>
+          <t>https://www.stepi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>한국환경연구원</t>
+          <t>국가과학기술인력개발원</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.kei.re.kr/menu.es?mid=a10308010000</t>
+          <t>https://www.kird.re.kr/</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>News Letter 뉴스레터 KEI 소식을 매달 종합하여 알려드립니다</t>
+          <t>https://www.kird.re.kr/notificationSpace/notice</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>강원대학교병원</t>
+          <t>국가생명윤리정책원</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.knuh.or.kr/hospitalinfo/hospitalinfo_03_01_list.asp</t>
+          <t>https://nibp.kr/</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>https://nibp.kr/board/notice</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>경제인문사회연구회</t>
+          <t>국가수리과학연구소</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.nrc.re.kr/menu.es?mid=a12001300000</t>
+          <t>http://www.nims.re.kr/</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>연설문</t>
+          <t>https://www.nims.re.kr/promote/post/news</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>국방기술품질원</t>
+          <t>국가아동권리보장원</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.dtaq.re.kr/ko/notice/seminar.jsp</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>세미나/신청</t>
+          <t>https://www.ncrc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>대외경제정책연구원</t>
+          <t>국가유산진흥원</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.kiep.go.kr/board.es?mid=a10508010000&amp;bid=0032&amp;cg_code=C01</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>KIEP 뉴스레터</t>
+          <t>https://www.kh.or.kr/</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>서울요양원</t>
+          <t>국가철도공단</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/PressReleases</t>
+          <t>https://www.kr.or.kr/</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>보도자료 더보기</t>
+          <t>https://www.kr.or.kr/boardCnts/list.do?boardID=51</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>아시아·태평양경제협력체 기후센터</t>
+          <t>국가평생교육진흥원</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.apcc21.org/board/BBSMSTR_000000000002?lang=ko</t>
+          <t>https://www.nile.or.kr/</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>연구보고서</t>
+          <t>https://www.nile.or.kr/usr/wap/list.do?app=11626&amp;listAll=Y&amp;lang=ko</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>한국건강가정진흥원</t>
+          <t>국립공원공단</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.kihf.or.kr/web/lay1/program/S1T81C297/public/list.do?rows=10&amp;page_unit=0</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>국민토론방</t>
+          <t>https://www.knps.or.kr/</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>한국고전번역원</t>
+          <t>국립광주과학관</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.itkc.or.kr/bbs/board.do?id=76&amp;menuId=86</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>고전번역연감</t>
+          <t>https://www.sciencecenter.or.kr/</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>한국고전번역원</t>
+          <t>국립낙동강생물자원관</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.itkc.or.kr/bbs/board.do?id=74&amp;menuId=10161</t>
+          <t>https://www.nnibr.re.kr/</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>전자저널</t>
+          <t>https://www.nnibr.re.kr/index.do?menu_id=00000341</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>한국고전번역원</t>
+          <t>국립농업박물관</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.itkc.or.kr/bbs/board.do?id=101&amp;menuId=10062</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>전체</t>
+          <t>https://namuk.or.kr/</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>국립대구과학관</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.at.or.kr/article/apko317100/list.action</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>법령</t>
+          <t>https://www.dnsm.or.kr/</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>국립박물관문화재단</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.at.or.kr/article/apko318000/list.action</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>사규 제정 ‧ 개정 예고</t>
+          <t>https://www.nmf.or.kr/</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>한국농수산식품유통공사</t>
+          <t>국립부산과학관</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.at.or.kr/article/apko344800/list.action</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>사업 실명제</t>
+          <t>http://www.sciport.or.kr/</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>한국주택금융공사</t>
+          <t>국립생태원</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.hf.go.kr/ko/sub04/sub04_05_02.do</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>공모전</t>
+          <t>http://www.nie.re.kr/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>한국체육산업개발(주)</t>
+          <t>국립아시아문화전당재단</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.ksponco.or.kr/menu.es?mid=a10201020000</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>설문참여</t>
+          <t>https://www.accf.or.kr/</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>한국해외인프라도시개발지원공사</t>
+          <t>국립암센터</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.kindkorea.or.kr/business/infra_office?board=17</t>
+          <t>https://www.ncc.re.kr/</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>폴란드</t>
+          <t>https://www.ncc.re.kr/eduboard.ncc?uri=edubbs002</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>(사)남북교류협력지원협회</t>
+          <t>국립울진해양과학관</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://sonosa.or.kr/?menuno=13</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>공지사항 바로가기</t>
+          <t>https://www.kosm.or.kr/</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>(재)우체국금융개발원</t>
+          <t>국립인천해양박물관</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.posid.or.kr/cyberpr/notice_list.do</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.inmm.or.kr/</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>(재)우체국시설관리단</t>
+          <t>국립중앙의료원</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.poma.or.kr/poma/notice.do</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.nmc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>(재)축산환경관리원</t>
+          <t>국립항공박물관</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.lemi.or.kr/board.do?boardno=24&amp;menuno=71</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://wwww.aviation.or.kr/</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>(재)한국보건의료정보원</t>
+          <t>국립해양박물관</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.khis.kr/menu.es?mid=a10301000000</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.mmk.or.kr/</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>건축공간연구원</t>
+          <t>국립해양생물자원관</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.auri.re.kr/menu.es?mid=a10401010000</t>
+          <t>https://www.mabik.re.kr/</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.mabik.re.kr/bbs/BBSMSTR_000000000331.do</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>공간정보품질관리원</t>
+          <t>국립호남권생물자원관</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.siqms.or.kr/M2001000/board.do</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://hnibr.re.kr/</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>국가과학기술인력개발원</t>
+          <t>국민건강보험공단</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.kird.re.kr/notificationSpace/notice</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.nhis.or.kr/</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>국가생명윤리정책원</t>
+          <t>국민건강보험공단 일산병원</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://nibp.kr/board/notice</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.nhimc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>국가수리과학연구소</t>
+          <t>국민연금공단</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.nims.re.kr/noticeYard/post/notification</t>
+          <t>https://www.nps.or.kr/</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.nps.or.kr/pnsgdnc/nscvrgdata/getOHAE0002M0List.do?menuId=MN24000898</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>국가수리과학연구소</t>
+          <t>국방과학연구소</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.nims.re.kr/post/equipNotice</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>장비공동활용 공지사항</t>
+          <t>https://www.add.re.kr/</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>국립인천해양박물관</t>
+          <t>국방기술진흥연구소</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.inmm.or.kr/doc/ko/selectDocList.do?menuSeq=3598&amp;bbsSeq=153</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.krit.re.kr/</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>국립중앙의료원</t>
+          <t>국방기술품질원</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.nmc.or.kr/nmc/board/B0000001</t>
+          <t>https://www.dtaq.re.kr/</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.dtaq.re.kr/ko/notice/notice.jsp</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>국립해양생물자원관</t>
+          <t>국방전직교육원</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.mabik.re.kr/bbs/BBSMSTR_000000000345/list.do</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.moti.or.kr/</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>국제식물검역인증원</t>
+          <t>국악방송</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.ipab.or.kr/kor/CMS/Board/Board.do?mCode=MN068</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.igbf.kr/</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>국토연구원</t>
+          <t>국제방송교류재단</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.krihs.re.kr/menu.es?mid=a10604000000</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.arirang.com/</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>극지연구소</t>
+          <t>국제식물검역인증원</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.kopri.re.kr/kopri/html/comm/0401.html</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.ipab.or.kr/</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>농림식품기술기획평가원</t>
+          <t>국토교통과학기술진흥원</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.ipet.re.kr/Market/MarketNoticeLV.asp</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kaia.re.kr/</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>농업정책보험금융원</t>
+          <t>국토안전관리원</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.apfs.kr/front/board/boardContentsListPage.do?boardId=10026&amp;menuId=41</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.kalis.or.kr/</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>농업정책보험금융원</t>
+          <t>국토연구원</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.apfs.kr/front/board/boardContentsListPage.do?boardId=10026&amp;menuId=5386&amp;selTab=1</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.krihs.re.kr/</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>농업정책보험금융원</t>
+          <t>그랜드코리아레저(주)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.apfs.kr/front/board/boardContentsListPage.do?boardId=10026&amp;menuId=5401&amp;selTab=3</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.grandkorea.com/</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>농업정책보험금융원</t>
+          <t>극지연구소</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.apfs.kr/front/board/boardContentsListPage.do?boardId=10026&amp;menuId=5478&amp;selTab=7</t>
+          <t>https://www.kopri.re.kr/</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>http://www.kopri.re.kr/_prog/bbs/?mode=V&amp;site_dvs_cd=kopri&amp;menu_dvs_cd=0402&amp;code=0502&amp;no=e1810153ce6b2b855717f743c6fc4616&amp;GotoPage=1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>농업정책보험금융원</t>
+          <t>근로복지공단</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.apfs.kr/front/board/boardContentsListPage.do?boardId=20093&amp;menuId=5491</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>신규 합격자 공지사항</t>
+          <t>https://www.comwel.or.kr/</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>대구경북첨단의료산업진흥재단</t>
+          <t>기술보증기금</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.kmedihub.re.kr/index.do?menu_id=00000063</t>
+          <t>https://www.kibo.or.kr/</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.kibo.or.kr/main/board/boardType107.do</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>대외경제정책연구원</t>
+          <t>기초과학연구원</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.kiep.go.kr/menu.es?mid=a10501000000</t>
+          <t>http://ibs.re.kr/</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://ibs.re.kr/cop/bbs/BBSMSTR_000000001033/selectBoardList.do</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>대한법률구조공단</t>
+          <t>노사발전재단</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.klac.or.kr/notification/notice/selectNoticeList.do?boardCode=32</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.nosa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>대한석탄공사</t>
+          <t>농림수산식품교육문화정보원</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.kocoal.or.kr/board/board_list.php?board_name=news&amp;search_category=공지사항</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.epis.or.kr/</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>대한적십자사</t>
+          <t>농림식품기술기획평가원</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.redcross.or.kr/main/pt/pst/selectPstInfo.do?mi=1009&amp;pstSn=504310&amp;bbsId=1001</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>공지사항 본사 2026년 대한적십자사 공공데이터 개방 및 활성화를 위한 설문조사 2026-07-27</t>
+          <t>https://www.ipet.re.kr/</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>대한적십자사</t>
+          <t>농업정책보험금융원</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://www.redcross.or.kr/main/pt/pst/selectPstList.do?mi=1009&amp;bbsId=1001</t>
+          <t>https://www.apfs.kr/</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.apfs.kr/front/board/boardContentsListPage.do?boardId=20093&amp;menuId=5491</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>대한적십자사</t>
+          <t>대구경북첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.redcross.or.kr/main/pt/pst/selectPstList.do?mi=2524&amp;bbsId=1513</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>RCY공지사항</t>
+          <t>https://www.kmedihub.re.kr/</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>동북아역사재단</t>
+          <t>대외경제정책연구원</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.nahf.or.kr/web/portal/bbs/1978/list</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>공지사항 더 보기</t>
+          <t>https://www.kiep.go.kr/</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
+          <t>대한무역투자진흥공사</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://busanpa.com/index.bpa?menuCd=DOM_000000105001000000</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.kotra.or.kr/</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
+          <t>대한법률구조공단</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://busanpa.com/index.bpa?menuCd=DOM_000000106002001007</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>선박저속운항프로그램 공지사항</t>
+          <t>https://www.klac.or.kr/</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>부산항만공사</t>
+          <t>대한석탄공사</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://busanpa.com/index.bpa?menuCd=DOM_000000106003003013</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kocoal.or.kr/</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>분당서울대학교병원</t>
+          <t>대한장애인체육회</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.snubh.org/intro/news/noti/list.do</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.koreanpc.kr/</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>산업연구원</t>
+          <t>대한적십자사</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.kiet.re.kr/communicate/ntcList</t>
+          <t>https://www.redcross.or.kr/</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.redcross.or.kr/main/pt/pst/selectPstList.do?mi=2524&amp;bbsId=1513</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>선박해양플랜트연구소</t>
+          <t>대한체육회</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.kriso.re.kr/menu.es?mid=a10401000000</t>
+          <t>https://www.sports.or.kr/</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.sports.or.kr/sports/bbs/BMSR00017/list.do?menuNo=200023</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>스포츠윤리센터</t>
+          <t>독립기념관</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.k-sec.or.kr/ste/page.do?bId=5&amp;type=B</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.i815.or.kr/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>시청자미디어재단</t>
+          <t>동남권원자력의학원</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://kcmf.or.kr/KCMF/contents/KCMF020100.do</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.dirams.re.kr/</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>시청자미디어재단</t>
+          <t>동북아역사재단</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://kcmf.or.kr/KCMF/contents/KCMF050107.do</t>
+          <t>https://www.nahf.or.kr/</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.nahf.or.kr/web/portal/bbs/1978/list</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>시청자미디어재단</t>
+          <t>무역안보관리원</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://kcmf.or.kr/KCMF/contents/KCMF050307.do</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kosti.or.kr/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>양육비이행관리원</t>
+          <t>민주화운동기념사업회</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.childsupport.or.kr/lay1/program/S1T27C28/front/board.do?sa=list&amp;bid=1</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kdemo.or.kr/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>에너지경제연구원</t>
+          <t>부산대학교병원</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.keei.re.kr/menu.es?mid=a10201010000</t>
+          <t>http://www.pnuh.or.kr/</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>http://www.pnuh.or.kr/pnuh/hospital/forum/notice.do</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>부산대학교치과병원</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.kdic.or.kr/di/pbcr/selectPbcrNtcList.do</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.pnudh.co.kr/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>예금보험공사</t>
+          <t>부산항만공사</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.kdic.or.kr/di/relsite/selectPbcrKrncNtcList.do</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://busanpa.com/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>예술의전당</t>
+          <t>북한이탈주민지원재단</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.sac.or.kr/site/main/board/academy/list</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>아카데미 공지사항</t>
+          <t>https://www.koreahana.or.kr/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>예술의전당</t>
+          <t>분당서울대학교병원</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.sac.or.kr/site/main/board/sacnews/list</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.snubh.org/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>오송첨단의료산업진흥재단</t>
+          <t>사립학교교직원연금공단</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.kbiohealth.kr/menu.es?mid=a10301000000</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.tp.or.kr/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>울산항만공사</t>
+          <t>산업연구원</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.upa.or.kr/portal/contents.do?mid=0601000000</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kiet.re.kr/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>의료기관평가인증원</t>
+          <t>새만금개발공사</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.koiha.or.kr/web/kr/community/notice_board.do</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>공지사항 더보기 +</t>
+          <t>https://www.sdco.or.kr/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>(재)한국우편사업진흥원</t>
+          <t>서민금융진흥원</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.posa.or.kr/portal/bbs/B0000008/list.do?menuNo=200020</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>https://www.kinfa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>게임물관리위원회</t>
+          <t>서울대학교병원</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.grac.or.kr/board/Inform.aspx</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>http://snuh.org/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>서울올림픽기념국민체육진흥공단</t>
+          <t>서울대학교치과병원</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.kspo.or.kr/kspo/qestnar/qustnr/list.do?menuNo=200010</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>http://www.snudh.org/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>축산물품질평가원</t>
+          <t>서울올림픽기념국민체육진흥공단</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.ekape.or.kr/board/list.do?menuId=menu149208&amp;boardInfoNo=0024</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kspo.or.kr/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>한국가스공사</t>
+          <t>서울요양원</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.kogas.or.kr/site/koGas/referenceBidList.do?Key=1050105000000</t>
+          <t>https://www.서울요양원.kr/</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.xn--2i4bo5fgwadewe.kr/sgcf/SGCFNews/Notice</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>한국공예디자인문화진흥원</t>
+          <t>선박해양플랜트연구소</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.kcdf.or.kr/brd/board/314/L/menu/282</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kriso.re.kr/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>한국과학창의재단</t>
+          <t>세종학당재단</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.kosac.re.kr/menus/270/boards/386/posts</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.ksif.or.kr/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>한국교통연구원</t>
+          <t>소상공인시장진흥공단</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.koti.re.kr/user/bbs/noticeList.do</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.semas.or.kr/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>한국국제보건의료재단</t>
+          <t>소프트웨어정책연구소</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.kofih.org/web/lay1/bbs/S1T10C21/A/1/list.do</t>
+          <t>https://www.spri.kr/</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.spri.kr/posts?code=notice</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>한국기상산업기술원</t>
+          <t>수도권매립지관리공사</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.kmiti.or.kr/kr/board/kmi_notice/boardList.do</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.slc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>한국농업기술진흥원</t>
+          <t>스포츠윤리센터</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.koat.or.kr/board/notice/list.do</t>
+          <t>https://www.k-sec.or.kr/</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.k-sec.or.kr/ste/page.do?bId=5&amp;type=B</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>한국등산·트레킹지원센터</t>
+          <t>시청자미디어재단</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://komount.or.kr/board/list.do?boardCode=B01</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kcmf.or.kr/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>한국로봇산업진흥원</t>
+          <t>식품안전정보원</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.kiria.org/portal/info/portalInfoNotiList.do;jsessionid=424C4290027EC3C39E20C8C3DAD703C9</t>
+          <t>http://www.foodinfo.or.kr/</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.foodinfo.or.kr/community</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>한국문학번역원</t>
+          <t>신용보증기금</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.ltikorea.or.kr/kr/board/notice/boardList.do</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.kodit.co.kr/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>한국문화예술교육진흥원</t>
+          <t>신용보증재단중앙회</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://arte.or.kr/information/notice/Notice_BoardList.do</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.koreg.or.kr/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>한국문화진흥주식회사</t>
+          <t>아시아·태평양경제협력체 기후센터</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://newseoulgolf.co.kr/board/list1.asp</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.apcc21.org/</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>한국방송통신전파진흥원</t>
+          <t>양육비이행관리원</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.kca.kr/boardList.do?boardId=NOTICE&amp;pageId=www47</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.childsupport.or.kr/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>한국법제연구원</t>
+          <t>에너지경제연구원</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.klri.re.kr/kor/survey/list.do</t>
+          <t>https://www.keei.re.kr/</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>설문조사</t>
+          <t>https://www.keei.re.kr/menu.es?mid=a10201010000</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>여수광양항만공사</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.kvic.or.kr/notice</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>https://www.ygpa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>한국보건사회연구원</t>
+          <t>연구개발특구진흥재단</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.kihasa.re.kr/news/notice</t>
+          <t>https://www.innopolis.or.kr/</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.innopolis.or.kr/board?menuId=MENU00318&amp;siteId=null</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>한국석유관리원</t>
+          <t>영상물등급위원회</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.kpetro.or.kr/lay1/program/S1T48C50/poll/list.do</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>https://www.kmrb.or.kr/</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>한국수자원조사기술원</t>
+          <t>영화진흥위원회</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://www.kihs.re.kr/kor_sub/bbs/notice_list.do</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kofic.or.kr/</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>한국스포츠레저(주)</t>
+          <t>예금보험공사</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.kospole.co.kr/toto/board/pr</t>
+          <t>https://www.kdic.or.kr/</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.kdic.or.kr/di/pbcr/selectPbcrNtcList.do</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>한국에너지정보문화재단</t>
+          <t>예술의전당</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://e-policy.or.kr/web/lay1/bbs/S1T16C17/A/1/list.do</t>
+          <t>https://www.sac.or.kr/</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.sac.or.kr/site/main/board/academy/list</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>한국여성과학기술인육성재단</t>
+          <t>오송첨단의료산업진흥재단</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.wiset.or.kr/prog/qustnr/kor/sub02_05_02/list.do</t>
+          <t>https://www.kbiohealth.kr/</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>설문참여</t>
+          <t>https://www.kbiohealth.kr/menu.es?mid=a10301000000</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>한국원자력안전기술원</t>
+          <t>울산항만공사</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.kins.re.kr/notice</t>
+          <t>https://www.upa.or.kr/</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.upa.or.kr/info/contents.do?mid=0800000000</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>한국원자력안전재단</t>
+          <t>육아정책연구소</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.kofons.or.kr/web/cop/bbsWeb/selectBoardList.do?bbsId=BBSMSTR_000000000431</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kicce.re.kr/</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>한국원자력의학원</t>
+          <t>의료기관평가인증원</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.kirams.re.kr/board/surveyForm2.do</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>https://www.koiha.or.kr/</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>한국장애인개발원</t>
+          <t>인천국제공항공사</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.koddi.or.kr/bbs/notice01.jsp</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.airport.kr/</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>한국저작권보호원</t>
+          <t>인천항만공사</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.kcopa.or.kr/lay1/bbs/S1T12C49/A/12/list.do</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://icpa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>한국저작권위원회</t>
+          <t>자동차손해배상진흥원</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.copyright.or.kr/customer-center/survey/list.do</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>https://www.tacss.or.kr/</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>한국조세재정연구원</t>
+          <t>재단법인 건설기술교육원</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.kipf.re.kr/kor/Customer/Survey/kipoll/list.do</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>https://www.kicte.or.kr/</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>재단법인 대한건설기계안전관리원</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://www.kywa.or.kr/pressinfo/notice_list.jsp</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kcesi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>한국탄소산업진흥원</t>
+          <t>재단법인 장애인기업종합지원센터</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.kcarbon.or.kr/bbs/board.php?bo_id=notice</t>
+          <t>http://www.debc.or.kr/</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.debc.or.kr/bbs/board.php?bo_table=s2_1</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>한국해양과학기술원</t>
+          <t>재단법인 한국공공조직은행</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.kiost.ac.kr/cop/bbs/BBSMSTR_000000000072/selectBoardList.do</t>
+          <t>https://kptb.kr/</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://kptb.kr/subpage_0501.asp</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>한국행정연구원</t>
+          <t>재단법인 한국에너지재단</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.kipa.re.kr/html/kor/cmn/bbs/cmnBbsGenList.do</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.koref.or.kr/</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>재단법인 한국자활복지개발원</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://www.keco.or.kr/web/lay1/bbs/S1T10C108/A/18/list.do</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kdissw.or.kr/</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>한식진흥원</t>
+          <t>재단법인 한국장기조직기증원</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.hansik.or.kr/board/no/list/001?menuSn=31</t>
+          <t>https://www.koda1458.kr/</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.koda1458.kr/communication/notices</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>한전KPS(주)</t>
+          <t>재외동포협력센터</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.kps.co.kr/web/communication/kpsnews/notice.do</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.okocc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>재단법인 장애인기업종합지원센터</t>
+          <t>전국재해구호협회</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.debc.or.kr/bbs/board.php?bo_table=s2_7</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://hopebridge.or.kr/</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>재단법인 한국장기조직기증원</t>
+          <t>전남대학교병원</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.koda1458.kr/communication/notices</t>
+          <t>http://www.cnuh.com/</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.cnuh.com/board/B0011.cs?m=63</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>제주대학교병원</t>
+          <t>전북대학교병원</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.jejunuh.co.kr/bbs/BBSMSTR_000000000061/list.do;jsessionid=C90353EE9DB92E20B389F341DCC720FB</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.jbuh.co.kr/</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>한국국제교류재단</t>
+          <t>전쟁기념사업회</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.kf.or.kr/kf/na/ntt/selectNttList.do?mi=1131&amp;bbsId=1051</t>
+          <t>https://www.warmemo.or.kr/</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.warmemo.or.kr:8443/Home/H40000/H40200/H40201/boardList</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>한국발명진흥회</t>
+          <t>정보통신기획평가원</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.kipa.org/kipa/notice/kw_0404.jsp</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>유관기관공지사항</t>
+          <t>http://www.iitp.kr/</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>한국의료분쟁조정중재원</t>
+          <t>정보통신산업진흥원</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://www.k-medi.or.kr/web/lay1/bbs/S1T13C18/A/1/list.do</t>
+          <t>https://www.nipa.kr/</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.nipa.kr/home/2-1</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>한국전력거래소</t>
+          <t>정보통신정책연구원</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.kpx.or.kr/board.es?mid=a11201000000&amp;bid=0042</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>http://www.kisdi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>한국지식재산보호원</t>
+          <t>정부법무공단</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.koipa.re.kr/home/board/brdList.do?menu_cd=000045</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>http://www.kgls.or.kr/</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>한국콘텐츠진흥원</t>
+          <t>제주국제자유도시개발센터</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.kocca.kr/kocca/bbs/list/B0000137.do?menuNo=204802</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.jdcenter.com/</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>한국특허전략개발원</t>
+          <t>제주대학교병원</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.kista.re.kr/user/board.do?bbsId=BBSMSTR_000000000532</t>
+          <t>https://www.jejunuh.co.kr/</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.jejunuh.co.kr/main/sub01_05_05.do</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>항공안전기술원</t>
+          <t>주식회사 에스알</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.kiast.or.kr/kr/cop/bbs/BBSMSTR_000000000031/selectBoardList.do</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.srail.or.kr/</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>한국형사·법무정책연구원</t>
+          <t>주택관리공단(주)</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.kicj.re.kr/board.es?mid=a10301000000&amp;bid=0009</t>
+          <t>https://www.kohom.or.kr/</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>공지사항 바로가기</t>
+          <t>https://www.kohom.or.kr/web/mainComm/HM002001.do</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>(주)강원랜드</t>
+          <t>주택도시보증공사</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://kangwonland.high1.com/kangwonland/selectQestnarList.do?key=2125</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>공공데이터 설문조사</t>
+          <t>https://www.khug.or.kr/</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>한국항로표지기술원</t>
+          <t>중소기업기술정보진흥원</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.katon.or.kr/article/notice/list</t>
+          <t>https://www.tipa.or.kr/</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>more 공지사항 더 보기</t>
+          <t>https://www.tipa.or.kr/s0401</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>자동차손해배상진흥원</t>
+          <t>중소기업은행</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.tacss.or.kr/notification/notice.jsp</t>
+          <t>http://www.ibk.co.kr/</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>공지사항 자동차보험/자동차공제 관련 정책변경, 자동차공제조합 관련 교육진행 등 공식적으로 안내할 사항을 제공합니다.</t>
+          <t>https://www.ibk.co.kr/cyber/noticeDataListCyber.ibk?pageId=IR03010500</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>소프트웨어정책연구소</t>
+          <t>중소벤처기업연구원</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.spri.kr/posts?code=notice</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>알림</t>
+          <t>https://www.kosi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>전쟁기념사업회</t>
+          <t>중소벤처기업진흥공단</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.warmemo.or.kr:8443/Home/H40000/H40200/H40201/boardList</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>알림</t>
+          <t>https://www.kosmes.or.kr/</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>새만금개발공사</t>
+          <t>중앙사회서비스원</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.sdco.or.kr/menu.es?mid=a10601010000</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>새소식</t>
+          <t>https://www.kcpass.or.kr/</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>중소벤처기업연구원</t>
+          <t>차세대수치예보모델개발사업단</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.kosi.re.kr/front/functionDisplay?menuFrontNo=78602310172731705597633385694148844092&amp;menuFrontURL=/front/webZineList</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>소식지</t>
+          <t>https://www.kiaps.org/</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>국가유산진흥원</t>
+          <t>창업진흥원</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://www.kh.or.kr/brd/board/1076/L/menu/1077</t>
+          <t>https://www.kised.or.kr/</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>주요알림</t>
+          <t>https://www.kised.or.kr/menu.es?mid=a10301000000</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>인천항만공사</t>
+          <t>축산물품질평가원</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.icpa.or.kr/main.do?menuKey=66</t>
+          <t>https://www.ekape.or.kr/</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>설문조사</t>
+          <t>https://www.ekape.or.kr/board/list.do?menuId=menu149208</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>재단법인 한국자활복지개발원</t>
+          <t>충남대학교병원</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.kdissw.or.kr/menu.es?mid=a10501010000</t>
+          <t>https://www.cnuh.co.kr/</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.cnuh.co.kr/bbs/notice/list.do</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>한국건강증진개발원</t>
+          <t>충북대학교병원</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.khepi.or.kr/menu?menuId=MENU00904</t>
+          <t>http://www.cbnuh.or.kr/</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>알림마당</t>
+          <t>https://www.cbnuh.or.kr/bbs/BBSMSTR_000000000355/list.do</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>한국공항공사</t>
+          <t>코레일관광개발(주)</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.airport.co.kr/www/cms/frCon/index.do?MENU_ID=1100</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.korailtravel.com/</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>한국과학기술기획평가원</t>
+          <t>코레일네트웍스(주)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.kistep.re.kr/menu.es?mid=a10402000000</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.korailnetworks.com/</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>한국관광공사</t>
+          <t>코레일로지스(주)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://knto.or.kr/customerFaq</t>
+          <t>https://www.koraillogis.com/</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>국민참여</t>
+          <t>https://www.koraillogis.com/support/notice.php</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>한국광해광업공단</t>
+          <t>코레일유통(주)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.komir.or.kr/kor/article/ATCL0d04c2e44</t>
+          <t>https://www.korailretail.com/</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.korailretail.com/bbs/selectBbsList.do?bbsId=BBSMSTR_000000000001</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>한국노동연구원</t>
+          <t>코레일테크(주)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.kli.re.kr/menu.es?mid=a10302000000</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.korailtech.com/</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>한국농어촌공사</t>
+          <t>태권도진흥재단</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.ekr.or.kr/index.krc?contentUid=402880317cc0644a017cc0c8a1be0116</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>https://www.tpf.or.kr/</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>한국농촌경제연구원</t>
+          <t>통일연구원</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.krei.re.kr/krei/page/23</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kinu.or.kr/</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>한국동서발전(주)</t>
+          <t>학교법인한국폴리텍</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.ewp.co.kr/kor/subpage/content.html?pc=6DP9QZAJ0UTZYGSTBXZM2LIV6V25JGP</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>http://www.kopo.ac.kr/</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>한국산업기술기획평가원</t>
+          <t>한국가스공사</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.keit.re.kr/menu.es?mid=a10301010000</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kogas.or.kr/</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>한국산업기술진흥원</t>
+          <t>한국가스안전공사</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.kiat.or.kr/front/user/newsMail.do</t>
+          <t>https://www.kgs.or.kr/</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>소식받기</t>
+          <t>https://www.kgs.or.kr/kgs/aga/board.do</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>한국산업인력공단</t>
+          <t>한국개발연구원</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.hrdkorea.or.kr/3/1/1</t>
+          <t>https://www.kdi.re.kr/</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.kdi.re.kr/share/noticeList</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>한국영유아보육·교육진흥원</t>
+          <t>한국건강가정진흥원</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.kicece.or.kr/kcpi/community/survey.do</t>
+          <t>http://www.kihf.or.kr/</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>설문조사</t>
+          <t>https://www.kihf.or.kr/web/lay1/bbs/S1T838C74/A/5/list.do?rows=10&amp;cpage=1</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>한국자산관리공사</t>
+          <t>한국건강증진개발원</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.kamco.or.kr/portal/contents.do?mId=0406050000</t>
+          <t>https://www.khepi.or.kr/</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.khepi.or.kr/menu?menuId=MENU00904</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>한국장애인고용공단</t>
+          <t>한국고용노동교육원</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.kead.or.kr/bbs/cntrbt/bbsPage.do?menuId=MENU0713</t>
+          <t>https://www.keli.kr/</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.keli.kr/info/pltfm/bbs/113/list.do</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>한국전력기술주식회사</t>
+          <t>한국고용정보원</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.kepco-enc.com/menu.es?mid=a10205050000</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>https://keis.or.kr/</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>한국제품안전관리원</t>
+          <t>한국고전번역원</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.kips.kr/cntns/cntns.do?menuSn=5010</t>
+          <t>https://www.itkc.or.kr/</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.itkc.or.kr/bbs/board.do?id=2&amp;menuId=99</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>한전KDN</t>
+          <t>한국공예디자인문화진흥원</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.kdn.com/menu.kdn?mid=a10111050000</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.kcdf.or.kr/</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>한전원자력연료주식회사</t>
+          <t>한국공정거래조정원</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.knfc.co.kr/menu?menuId=MENU00302</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>알림마당</t>
+          <t>https://www.kofair.or.kr/</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>한국도로공사</t>
+          <t>한국공항공사</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.ex.co.kr/partcptn</t>
+          <t>http://www.airport.co.kr/</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>국민참여로</t>
+          <t>https://www.airport.co.kr/www/cms/frCon/index.do?MENU_ID=550</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>한국투자공사</t>
+          <t>한국과학기술기획평가원</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.kic.kr/ko/news/announcements/bidding</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>공고·공지</t>
+          <t>https://www.kistep.re.kr/</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>국립해양박물관</t>
+          <t>한국과학창의재단</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.mmk.or.kr/?folder=bbs&amp;page=list&amp;board_id=notice</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>알림 더보기</t>
+          <t>https://www.kosac.re.kr/</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>대한체육회</t>
+          <t>한국관광공사</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.sports.or.kr/sports/bbs/BMSR00009/list.do?menuNo=200049</t>
+          <t>http://knto.or.kr/</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>체육단체소식</t>
+          <t>https://knto.or.kr/correctedNews</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>주택관리공단(주)</t>
+          <t>한국관세정보원</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.kohom.or.kr/web/mainComm/HM002001.do</t>
+          <t>https://kcits.or.kr/</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>공단 새소식</t>
+          <t>https://kcits.or.kr/news/noticeList</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>한전MCS(주)</t>
+          <t>한국광해광업공단</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.kepcomcs.co.kr/mber/esgsafety/safety/safetynews/bbs/6/list</t>
+          <t>https://www.komir.or.kr/</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>안전경영소식</t>
+          <t>https://www.komir.or.kr/kor/17/survey</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>국가평생교육진흥원</t>
+          <t>한국교육개발원</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.nile.or.kr/usr/wap/list.do?app=11762&amp;listAll=Y&amp;lang=ko</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>NILE 소식</t>
+          <t>https://www.kedi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>한국상하수도협회</t>
+          <t>한국교육과정평가원</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.kwwa.or.kr/kr/board/notify_12/boardList.do</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>소식지/기술지</t>
+          <t>https://www.kice.re.kr/</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>한국연구재단</t>
+          <t>한국교육학술정보원</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.nrf.re.kr/page/53?menuNo=53</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>NRF 공지사항</t>
+          <t>https://www.keris.or.kr/</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원</t>
+          <t>한국교통안전공단</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>공지사항 더보기</t>
+          <t>https://www.kotsa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>한국학중앙연구원</t>
+          <t>한국교통연구원</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>http://www.aks.ac.kr/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000130&amp;adiInfo9=A&amp;menuNo=4010180000</t>
+          <t>https://www.koti.re.kr/</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>온라인 소식지 신청</t>
+          <t>https://www.koti.re.kr/user/bbs/noticeList.do</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>노사발전재단</t>
+          <t>한국국방연구원</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.nosa.or.kr/portal/nosa/FoundNews/reportData?bltnNo=11788739696251</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>국민이 인공지능(AI)로 그린 노사발전재단 대표 캐릭터 선정 2026.09.07</t>
+          <t>https://www.kida.re.kr/</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>88관광개발(주)</t>
+          <t>한국국제교류재단</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.88countryclub.co.kr/Board/BoardList.aspx?cfgid=join</t>
+          <t>https://www.kf.or.kr/</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>조인게시판</t>
+          <t>https://www.kf.or.kr/kf/na/ntt/selectNttList.do?mi=1131&amp;bbsId=1051</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>한국방송광고진흥공사</t>
+          <t>한국국제보건의료재단</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.kobaco.co.kr/site/main/board/integrated_board/list</t>
+          <t>https://www.kofih.org/</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>통합게시판</t>
+          <t>https://www.kofih.org/web/lay1/bbs/S1T10C21/A/1/list.do</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>한국벤처투자</t>
+          <t>한국국제협력단</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.kvic.or.kr/notice/kvic-notice</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.koica.go.kr/</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>한국여성과학기술인육성재단</t>
+          <t>한국국토정보공사</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.wiset.or.kr/bbs/BBSMSTR_000000000304/list.do</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>공지사항</t>
+          <t>https://www.lx.or.kr/</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>한국저작권보호원</t>
+          <t>한국기상산업기술원</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.kcopa.or.kr/lay1/bbs/S1T239C240/A/60/list.do</t>
+          <t>https://www.kmiti.or.kr/</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>https://www.kmiti.or.kr/kr/board/kmi_notice/boardList.do</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>한국청소년활동진흥원</t>
+          <t>한국기술교육대학교</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.kywa.or.kr/community/actively_01_list.jsp</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>국민참여</t>
+          <t>https://www.koreatech.ac.kr/</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>한국환경공단</t>
+          <t>한국나노기술원</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.keco.or.kr/web/lay1/program/S1T217C222/poll/list.do</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>설문조사</t>
+          <t>https://www.kanc.re.kr/</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
+          <t>한국남동발전(주)</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>https://www.koenergy.kr/</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>한국남부발전(주)</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>https://www.kospo.co.kr/</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>한국노동연구원</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>https://www.kli.re.kr/</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>한국노인인력개발원</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>https://www.kordi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>한국농수산식품유통공사</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>https://www.at.or.kr/</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>https://www.at.or.kr/article/apko364000/list.action</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>한국농어촌공사</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>https://www.ekr.or.kr/</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>한국농업기술진흥원</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>https://www.koat.or.kr/</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>https://www.koat.or.kr/board/notice/list.do</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>한국농촌경제연구원</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>https://www.krei.re.kr/</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>https://www.krei.re.kr/krei/page/23</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>한국데이터산업진흥원</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>https://www.kdata.or.kr/</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>https://www.kdata.or.kr/kr/board/notice_01/boardList.do</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>한국도로공사</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>https://www.ex.co.kr/</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>한국도로공사서비스(주)</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>https://www.exservice.co.kr/</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>https://www.exservice.co.kr/boad/bd_notice/egolist.php?bd=2</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>한국도로교통공단</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>https://www.koroad.or.kr/</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>한국도박문제예방치유원</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>https://www.kcgp.or.kr/</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>한국동서발전(주)</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>https://www.ewp.co.kr/</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>한국등산·트레킹지원센터</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>https://komount.or.kr/</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>한국디자인진흥원</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>https://www.kidp.or.kr/</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>https://www.kidp.or.kr/?menuno=1019</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>한국로봇산업진흥원</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>https://www.kiria.org/</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>https://www.kiria.org/portal/info/portalInfoNotiList.do</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>한국마사회</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>https://www.kra.co.kr/</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>한국마약퇴치운동본부</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>https://drugfree.or.kr/</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>한국무역보험공사</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>https://www.ksure.or.kr/</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>https://www.ksure.or.kr/rh-kr/bbs/i-412/list.do</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>한국문학번역원</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>https://www.ltikorea.or.kr/</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>https://www.ltikorea.or.kr/kr/board/notice/boardList.do</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>한국문화관광연구원</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>http://www.kcti.re.kr/</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>한국문화예술교육진흥원</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>https://www.arte.or.kr/</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>https://arte.or.kr/information/notice/Notice_BoardList.do</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>한국문화예술위원회</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>https://www.arko.or.kr/</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>한국문화정보원</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>https://www.kcisa.kr/</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>https://www.kcisa.kr/kr/board/notice/boardList.do</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>한국문화진흥주식회사</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>https://newseoulgolf.co.kr/</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>한국물기술인증원</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>https://www.kwtc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>한국발명진흥회</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>https://www.kipa.org/</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>https://www.kipa.org/kipa/notice/kw_0404.jsp</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>한국방송광고진흥공사</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>https://www.kobaco.co.kr/</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>https://www.kobaco.co.kr/site/main/board/notice/list</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>한국방송통신전파진흥원</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>https://www.kca.kr/</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>https://www.kca.kr/boardList.do?boardId=NOTICE&amp;pageId=www47</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>한국법무보호복지공단</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>https://koreha.or.kr/</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>한국법제연구원</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>https://www.klri.re.kr/</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>https://www.klri.re.kr/kor/bbs/BBSMSTR_000000000001/list.do</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>한국벤처투자</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>https://www.kvic.or.kr/</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>https://www.kvic.or.kr/notice</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>한국보건복지인재원</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>https://www.kohi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>한국보건사회연구원</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>https://www.kihasa.re.kr/</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>https://www.kihasa.re.kr/news</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>한국보건산업진흥원</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>https://www.khidi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>https://www.khidi.or.kr/board?menuId=MENU02458</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>한국보건의료연구원</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>https://www.neca.re.kr/</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>한국보건의료인국가시험원</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>https://www.kuksiwon.or.kr/</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>한국보훈복지의료공단</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>https://www.bohun.or.kr/</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>https://www.bohun.or.kr/main/na/ntt/selectNttList.do?mi=32371&amp;bbsId=1152</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>한국부동산원</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>https://www.reb.or.kr/</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>https://www.reb.or.kr/reb/na/ntt/selectNttList.do?mi=9564&amp;bbsId=1134</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>한국사학진흥재단</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>https://www.kasfo.or.kr/</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>한국사회보장정보원</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>http://www.ssis.or.kr/</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>한국사회복지협의회</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>https://www.bokji.net/</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>한국사회적기업진흥원</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>https://www.socialenterprise.or.kr/</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>한국산림복지진흥원</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>https://www.fowi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>한국산업기술기획평가원</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>https://www.keit.re.kr/</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>https://www.keit.re.kr/menu.es?mid=a10301010000</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>한국산업기술시험원</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>https://www.ktl.re.kr/</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>한국산업기술진흥원</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>https://www.kiat.or.kr/</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>https://www.kiat.or.kr/front/user/newsMail.do</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>한국산업단지공단</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>https://www.kicox.or.kr/</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>한국산업안전보건공단</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>https://kosha.or.kr/</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>한국산업은행</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>http://www.kdb.co.kr/</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr"/>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>한국산업인력공단</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>https://www.hrdkorea.or.kr/</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>https://www.hrdkorea.or.kr/3/1/1?k=56118</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>한국상하수도협회</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>https://www.kwwa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr"/>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>한국생명존중희망재단</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>https://www.kfsp.or.kr/</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>https://www.kfsp.or.kr/home/kor/board.do?menuPos=62</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>한국서부발전(주)</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>https://www.iwest.co.kr/</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>한국석유공사</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>https://www.knoc.co.kr/</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>https://www.knoc.co.kr/sub11/sub11_1.jsp</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>한국석유관리원</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>http://www.kpetro.or.kr/</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>https://www.kpetro.or.kr/lay1/program/S1T55C65/sns/intro.do</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>한국세라믹기술원</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>https://www.kicet.re.kr/</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>한국소방산업기술원</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>https://www.kfi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>한국소비자원</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>https://www.kca.go.kr/</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>한국수력원자력(주)</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>https://www.khnp.co.kr/</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>한국수목원정원관리원</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>https://www.koagi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>https://www.koagi.or.kr/www/user/bbs/BD_selectBbsList.do?q_bbsSn=1001</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>한국수산자원공단</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>http://www.fira.or.kr/</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>한국수자원공사</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>https://www.kwater.or.kr/</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>https://www.kwater.or.kr/busi/sub03/noti01List.do?brdId=KO90&amp;s_mid=2084</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>한국수자원조사기술원</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>https://www.kihs.re.kr/</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr"/>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>한국수출입은행</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>https://www.koreaexim.go.kr/</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>한국스포츠레저(주)</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>https://www.kospole.co.kr/</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>한국승강기안전공단</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>https://home.koelsa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>https://home.koelsa.or.kr/portal/contents.do?mId=0404020000</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>한국식품산업클러스터진흥원</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>https://www.foodpolis.kr/</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>https://www.foodpolis.kr/web/info/notice/sub01.do</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>한국식품안전관리인증원</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>https://www.haccp.or.kr/</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>한국양성평등교육진흥원</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>http://www.kigepe.or.kr/</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>https://www.kigepe.or.kr/EgovMovePage.do?menuNo=13000</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>한국어촌어항공단</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://www.fipa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>한국언론진흥재단</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://www.kpf.or.kr/</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>한국에너지공단</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>http://www.energy.or.kr/</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>https://www.energy.or.kr/front/board/List3.do</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>한국에너지기술평가원</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://www.ketep.re.kr/</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>https://www.ketep.re.kr/board?menuId=MENU002070200000000&amp;boardId=BOARD00065</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>한국에너지정보문화재단</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://e-policy.or.kr/</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>https://e-policy.or.kr/web/lay1/bbs/S1T16C17/A/1/list.do</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>한국여성과학기술인육성재단</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://www.wiset.or.kr/</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>https://www.wiset.or.kr/bbs/BBSMSTR_000000000307/list.do</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>한국여성인권진흥원</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://www.stop.or.kr/</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr"/>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>한국여성정책연구원</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://www.kwdi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>한국연구재단</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://www.nrf.re.kr/</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>https://www.nrf.re.kr/page/53?menuNo=53</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>한국영상자료원</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://www.koreafilm.or.kr/</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>https://www.koreafilm.or.kr/kofa/news/notice</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>한국영유아보육·교육진흥원</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>http://www.kicece.or.kr/</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr"/>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>한국예술인복지재단</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>http://www.kawf.kr/</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr"/>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>한국원산지정보원</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>https://www.origin.or.kr/</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://www.origin.or.kr/lay1/bbs/S1T12C49/A/12/list.do</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>한국원자력안전기술원</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>https://www.kins.re.kr/</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://www.kins.re.kr/notice</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>한국원자력안전재단</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>https://www.kofons.or.kr/</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://www.kofons.or.kr/web/cop/bbsWeb/selectBoardList.do?bbsId=BBSMSTR_000000000431</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
           <t>한국원자력의학원</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>https://www.kirams.re.kr/board/generalBoardList1.do</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>소식/공지</t>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>https://www.kirams.re.kr/</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://www.kirams.re.kr/kirams/board/generalBoardList5.do</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>한국원자력통제기술원</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>https://www.kinac.re.kr/</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://www.kinac.re.kr/menu?menuId=MN0000000495</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>한국원자력환경공단</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>https://www.korad.or.kr/</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>한국의료기기안전정보원</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>http://www.nids.or.kr/</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>한국의료분쟁조정중재원</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>https://www.k-medi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>한국의약품안전관리원</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>https://www.drugsafe.or.kr/</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://www.drugsafe.or.kr/iwt/ds/ko/bbs/EgovBbs.do?bbsId=BBSMSTR_000000000011</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>한국인터넷진흥원</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr"/>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>한국임업진흥원</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>https://www.kofpi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr"/>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>한국자산관리공사</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>http://www.kamco.or.kr/</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr"/>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>한국잡월드</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>http://www.koreajobworld.or.kr/</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>한국장애인개발원</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>https://www.koddi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://www.koddi.or.kr/bbs/notice01.jsp</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>한국장애인고용공단</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>https://www.kead.or.kr/</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr"/>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>한국장학재단</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>https://www.kosaf.go.kr/</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>한국재정정보원</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>https://www.fis.kr/</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr"/>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>한국저작권보호원</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>https://www.kcopa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://www.kcopa.or.kr/lay1/bbs/S1T12C49/A/12/list.do</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>한국저작권위원회</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>https://www.copyright.or.kr/</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>한국전기안전공사</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>http://www.kesco.or.kr/</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>한국전력거래소</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>https://www.kpx.or.kr/</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>한국전력공사</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>https://kepco.co.kr/</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>한국전력국제원자력대학원대학교</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>https://kings.ac.kr/</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://kings.ac.kr/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000245</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>한국전력기술주식회사</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>https://www.kepco-enc.com/</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>한국제품안전관리원</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>https://www.kips.kr/</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr"/>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>한국조세재정연구원</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>https://www.kipf.re.kr/</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr"/>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>한국조폐공사</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>https://www.komsco.com/</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>한국주택금융공사</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>https://www.hf.go.kr/</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>준정부기관(기금관리형)</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>한국중부발전(주)</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>https://www.komipo.co.kr/</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>한국중소벤처기업유통원</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>https://www.kodma.or.kr/</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>한국지능정보사회진흥원</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>https://www.nia.or.kr/</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>한국지식재산보호원</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>https://www.koipa.re.kr/</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://www.koipa.re.kr/home/board/brdList.do?menu_cd=000052</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>한국지식재산연구원</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>https://www.kiip.re.kr/</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>한국지역난방공사</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>https://www.kdhc.co.kr/</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>공기업(시장형)</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>한국직업능력연구원</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>https://www.krivet.re.kr/</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr"/>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>한국철도공사</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>https://info.korail.com/</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr"/>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>한국청소년상담복지개발원</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>http://www.kyci.or.kr/</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr"/>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>한국청소년정책연구원</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>https://www.nypi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://www.nypi.re.kr/board?menuKey=D7eWzSzI7U&amp;siteId=SITE00002&amp;bbsId=BOARD00015</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>한국청소년활동진흥원</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>https://www.kywa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>한국체육산업개발(주)</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>https://www.ksponco.or.kr/</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>한국출판문화산업진흥원</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>http://www.kpipa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>한국치산기술협회</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>https://www.kafet.or.kr/</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>https://www.kocca.kr/</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://www.kocca.kr/kocca/bbs/list/B0159004.do?menuNo=204803</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>한국탄소산업진흥원</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>https://www.kcarbon.or.kr/</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://www.kcarbon.or.kr/bbs/board.php?bo_id=notice</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>한국토지주택공사</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>https://www.lh.or.kr/</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://www.lh.or.kr/menu.es?mid=a10601000000</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>한국투자공사</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>https://www.kic.kr/</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://kic.kr/ko/news/announcements/notice/svrvip</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>한국특허기술진흥원</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>https://www.kipro.or.kr/</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://www.kipro.or.kr/board/notice/list</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>한국특허전략개발원</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>https://www.kista.re.kr/</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>한국특허정보원</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>https://www.kipi.or.kr/</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr"/>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>한국학중앙연구원</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>http://www.aks.ac.kr/</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>http://www.aks.ac.kr/cop/bbs/selectBoardList.do?bbsId=BBSMSTR_000000000082&amp;menuNo=4010110000</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>한국한의약진흥원</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>https://www.nikom.or.kr/</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr"/>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>한국항로표지기술원</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>https://www.katon.or.kr/</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://www.katon.or.kr/article/tender_notice/list?pageIndex=7&amp;</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>한국해양과학기술원</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>https://www.kiost.ac.kr/</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://www.kiost.ac.kr/cop/bbs/BBSMSTR_000000000072/selectBoardList.do</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>한국해양교통안전공단</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>https://www.komsa.or.kr/</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr"/>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>한국해양수산개발원</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>https://www.kmi.re.kr/</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr"/>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>한국해양수산연수원</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>https://www.seaman.or.kr/</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr"/>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>한국해양조사협회</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>https://www.khra.kr/</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr"/>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>한국해양진흥공사</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>https://www.kobc.or.kr/</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr"/>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>한국해외인프라도시개발지원공사</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>https://www.kindkorea.or.kr/</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>한국행정연구원</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>https://www.kipa.re.kr/</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr"/>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>한국형사·법무정책연구원</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>http://www.kicj.re.kr/</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://www.kicj.re.kr/menu.es?mid=a10107010000</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>한국환경공단</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>https://www.keco.or.kr/</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>한국환경보전원</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>https://www.keci.or.kr/</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>한국환경산업기술원</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>https://www.keiti.re.kr/</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://www.keiti.re.kr/site/keiti/rnd/selectRndSubjectList.do</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>준정부기관(위탁집행형)</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>한국환경연구원</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>https://www.kei.re.kr/</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr"/>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>한식진흥원</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>https://www.hansik.or.kr/</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://www.hansik.or.kr/board/no/list/001?menuSn=31</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>한전KDN</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>https://www.kdn.com/</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://www.kdn.com/menu.kdn?mid=a10111050000</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>한전KPS(주)</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>https://www.kps.co.kr/</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://www.kps.co.kr/web/company/recruit/info/notice.do</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>한전MCS(주)</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>https://www.kepcomcs.co.kr/</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr"/>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>한전원자력연료주식회사</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>https://www.knfc.co.kr/</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://www.knfc.co.kr/menu?menuId=MENU00302</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>항공안전기술원</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>https://www.kiast.or.kr/</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://www.kiast.or.kr/kr/cop/bbs/BBSMSTR_000000000001/selectBoardList.do</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>해양수산과학기술진흥원</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>https://www.kimst.re.kr/</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>기타공공기관</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>해양환경공단</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>https://www.koem.or.kr/</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr"/>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>공기업(준시장형)</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>기존자료 복원</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <autoFilter ref="A1:E356"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/monitor_targets.xlsx
+++ b/monitor_targets.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E356"/>
+  <dimension ref="A1:G356"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,16 @@
           <t>URL상태</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>최종확인일</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -478,6 +488,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -490,7 +505,6 @@
           <t>http://www.gokams.or.kr/</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -499,6 +513,11 @@
       <c r="E3" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -528,6 +547,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -540,7 +564,6 @@
           <t>http://www.pola.or.kr/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -549,6 +572,11 @@
       <c r="E5" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -563,7 +591,6 @@
           <t>http://www.poma.or.kr/</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -572,6 +599,11 @@
       <c r="E6" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -601,6 +633,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -613,7 +650,6 @@
           <t>https://www.lemi.or.kr/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -622,6 +658,11 @@
       <c r="E8" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -651,6 +692,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -663,7 +709,6 @@
           <t>https://www.posa.or.kr/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -672,6 +717,11 @@
       <c r="E10" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -686,7 +736,6 @@
           <t>https://www.kosii.or.kr/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -695,6 +744,11 @@
       <c r="E11" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -709,7 +763,6 @@
           <t>https://www.stat.or.kr/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -718,6 +771,11 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -732,7 +790,6 @@
           <t>https://kangwonland.high1.com/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -741,6 +798,11 @@
       <c r="E13" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -755,7 +817,6 @@
           <t>https://www.gongyoung.kr/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -764,6 +825,11 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -778,7 +844,6 @@
           <t>https://www.kogas-tech.or.kr/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -787,6 +852,11 @@
       <c r="E15" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -801,7 +871,6 @@
           <t>https://www.88countryclub.co.kr/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -810,6 +879,11 @@
       <c r="E16" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -839,6 +913,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -866,6 +945,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -878,7 +962,6 @@
           <t>https://www.lhca.or.kr/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -887,6 +970,11 @@
       <c r="E19" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -916,6 +1004,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -928,7 +1021,6 @@
           <t>http://www.knudh.or.kr/</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -937,6 +1029,11 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -951,7 +1048,6 @@
           <t>https://www.hira.or.kr/</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -960,6 +1056,11 @@
       <c r="E22" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -974,7 +1075,6 @@
           <t>https://www.cw.or.kr/</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -983,6 +1083,11 @@
       <c r="E23" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1012,6 +1117,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1024,7 +1134,6 @@
           <t>https://www.grac.or.kr/</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1033,6 +1142,11 @@
       <c r="E25" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1161,6 @@
           <t>http://knuh.kr/</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1056,6 +1169,11 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1188,6 @@
           <t>https://www.knudh.kr/</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1079,6 +1196,11 @@
       <c r="E27" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1215,6 @@
           <t>http://www.gnuh.co.kr/</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1102,6 +1223,11 @@
       <c r="E28" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1131,6 +1257,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1143,7 +1274,6 @@
           <t>https://www.spacen.or.kr/</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1152,6 +1282,11 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1181,6 +1316,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1208,6 +1348,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1220,7 +1365,6 @@
           <t>https://www.compa.re.kr/</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1229,6 +1373,11 @@
       <c r="E33" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1392,6 @@
           <t>https://www.stepi.re.kr/</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1252,6 +1400,11 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1281,6 +1434,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1308,6 +1466,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1335,6 +1498,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1347,7 +1515,6 @@
           <t>https://www.ncrc.or.kr/</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1356,6 +1523,11 @@
       <c r="E38" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1542,6 @@
           <t>https://www.kh.or.kr/</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1379,6 +1550,11 @@
       <c r="E39" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1408,6 +1584,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1435,6 +1616,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1447,7 +1633,6 @@
           <t>https://www.knps.or.kr/</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -1456,6 +1641,11 @@
       <c r="E42" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1660,6 @@
           <t>https://www.sciencecenter.or.kr/</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1479,6 +1668,11 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1508,6 +1702,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1520,7 +1719,6 @@
           <t>https://namuk.or.kr/</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1529,6 +1727,11 @@
       <c r="E45" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1746,6 @@
           <t>https://www.dnsm.or.kr/</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1552,6 +1754,11 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1773,6 @@
           <t>https://www.nmf.or.kr/</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1575,6 +1781,11 @@
       <c r="E47" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1800,6 @@
           <t>http://www.sciport.or.kr/</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1598,6 +1808,11 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1827,6 @@
           <t>http://www.nie.re.kr/</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -1621,6 +1835,11 @@
       <c r="E49" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1854,6 @@
           <t>https://www.accf.or.kr/</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1644,6 +1862,11 @@
       <c r="E50" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1673,6 +1896,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1685,7 +1913,6 @@
           <t>https://www.kosm.or.kr/</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1694,6 +1921,11 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1940,6 @@
           <t>https://www.inmm.or.kr/</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1717,6 +1948,11 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1967,6 @@
           <t>https://www.nmc.or.kr/</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1740,6 +1975,11 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1994,6 @@
           <t>https://wwww.aviation.or.kr/</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1763,6 +2002,11 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1777,7 +2021,6 @@
           <t>https://www.mmk.or.kr/</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1786,6 +2029,11 @@
       <c r="E56" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1815,6 +2063,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1827,7 +2080,6 @@
           <t>http://hnibr.re.kr/</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1836,6 +2088,11 @@
       <c r="E58" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1850,7 +2107,6 @@
           <t>https://www.nhis.or.kr/</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -1859,6 +2115,11 @@
       <c r="E59" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1873,7 +2134,6 @@
           <t>https://www.nhimc.or.kr/</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -1882,6 +2142,11 @@
       <c r="E60" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1911,6 +2176,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1923,7 +2193,6 @@
           <t>https://www.add.re.kr/</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1932,6 +2201,11 @@
       <c r="E62" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1946,7 +2220,6 @@
           <t>https://www.krit.re.kr/</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -1955,6 +2228,11 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -1984,6 +2262,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1996,7 +2279,6 @@
           <t>https://www.moti.or.kr/</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2005,6 +2287,11 @@
       <c r="E65" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2019,7 +2306,6 @@
           <t>https://www.igbf.kr/</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2028,6 +2314,11 @@
       <c r="E66" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2042,7 +2333,6 @@
           <t>https://www.arirang.com/</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2051,6 +2341,11 @@
       <c r="E67" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2360,6 @@
           <t>https://www.ipab.or.kr/</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2074,6 +2368,11 @@
       <c r="E68" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2387,6 @@
           <t>https://www.kaia.re.kr/</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2097,6 +2395,11 @@
       <c r="E69" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2414,6 @@
           <t>http://www.kalis.or.kr/</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr"/>
       <c r="D70" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -2120,6 +2422,11 @@
       <c r="E70" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2441,6 @@
           <t>http://www.krihs.re.kr/</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2143,6 +2449,11 @@
       <c r="E71" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2468,6 @@
           <t>https://www.grandkorea.com/</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -2166,6 +2476,11 @@
       <c r="E72" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2195,6 +2510,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2207,7 +2527,6 @@
           <t>https://www.comwel.or.kr/</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -2216,6 +2535,11 @@
       <c r="E74" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2245,6 +2569,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2272,6 +2601,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2284,7 +2618,6 @@
           <t>https://www.nosa.or.kr/</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2293,6 +2626,11 @@
       <c r="E77" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2645,6 @@
           <t>https://www.epis.or.kr/</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2316,6 +2653,11 @@
       <c r="E78" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2330,7 +2672,6 @@
           <t>https://www.ipet.re.kr/</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2339,6 +2680,11 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2368,6 +2714,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2380,7 +2731,6 @@
           <t>https://www.kmedihub.re.kr/</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
       <c r="D81" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2389,6 +2739,11 @@
       <c r="E81" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2758,6 @@
           <t>https://www.kiep.go.kr/</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
       <c r="D82" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2412,6 +2766,11 @@
       <c r="E82" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2785,6 @@
           <t>http://www.kotra.or.kr/</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -2435,6 +2793,11 @@
       <c r="E83" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2812,6 @@
           <t>https://www.klac.or.kr/</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2458,6 +2820,11 @@
       <c r="E84" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2839,6 @@
           <t>https://www.kocoal.or.kr/</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr"/>
       <c r="D85" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2481,6 +2847,11 @@
       <c r="E85" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2866,6 @@
           <t>http://www.koreanpc.kr/</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr"/>
       <c r="D86" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2504,6 +2874,11 @@
       <c r="E86" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2533,6 +2908,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2560,6 +2940,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2572,7 +2957,6 @@
           <t>https://www.i815.or.kr/</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2581,6 +2965,11 @@
       <c r="E89" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2595,7 +2984,6 @@
           <t>https://www.dirams.re.kr/</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2604,6 +2992,11 @@
       <c r="E90" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2633,6 +3026,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2645,7 +3043,6 @@
           <t>https://www.kosti.or.kr/</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2654,6 +3051,11 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2668,7 +3070,6 @@
           <t>https://www.kdemo.or.kr/</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2677,6 +3078,11 @@
       <c r="E93" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2706,6 +3112,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2718,7 +3129,6 @@
           <t>https://www.pnudh.co.kr/</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2727,6 +3137,11 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2741,7 +3156,6 @@
           <t>https://busanpa.com/</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2750,6 +3164,11 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2764,7 +3183,6 @@
           <t>https://www.koreahana.or.kr/</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2773,6 +3191,11 @@
       <c r="E97" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2787,7 +3210,6 @@
           <t>https://www.snubh.org/</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2796,6 +3218,11 @@
       <c r="E98" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2810,7 +3237,6 @@
           <t>https://www.tp.or.kr/</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2819,6 +3245,11 @@
       <c r="E99" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2833,7 +3264,6 @@
           <t>https://www.kiet.re.kr/</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2842,6 +3272,11 @@
       <c r="E100" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2856,7 +3291,6 @@
           <t>https://www.sdco.or.kr/</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2865,6 +3299,11 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2879,7 +3318,6 @@
           <t>https://www.kinfa.or.kr/</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2888,6 +3326,11 @@
       <c r="E102" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2902,7 +3345,6 @@
           <t>http://snuh.org/</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
       <c r="D103" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2911,6 +3353,11 @@
       <c r="E103" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2925,7 +3372,6 @@
           <t>http://www.snudh.org/</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -2934,6 +3380,11 @@
       <c r="E104" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2948,7 +3399,6 @@
           <t>https://www.kspo.or.kr/</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr"/>
       <c r="D105" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -2957,6 +3407,11 @@
       <c r="E105" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -2986,6 +3441,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2998,7 +3458,6 @@
           <t>https://www.kriso.re.kr/</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3007,6 +3466,11 @@
       <c r="E107" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3485,6 @@
           <t>http://www.ksif.or.kr/</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3030,6 +3493,11 @@
       <c r="E108" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3512,6 @@
           <t>https://www.semas.or.kr/</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -3053,6 +3520,11 @@
       <c r="E109" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3082,6 +3554,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3094,7 +3571,6 @@
           <t>http://www.slc.or.kr/</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr"/>
       <c r="D111" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3103,6 +3579,11 @@
       <c r="E111" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3132,6 +3613,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3144,7 +3630,6 @@
           <t>https://www.kcmf.or.kr/</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3153,6 +3638,11 @@
       <c r="E113" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3182,6 +3672,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3194,7 +3689,6 @@
           <t>http://www.kodit.co.kr/</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -3203,6 +3697,11 @@
       <c r="E115" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3217,7 +3716,6 @@
           <t>http://www.koreg.or.kr/</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3226,6 +3724,11 @@
       <c r="E116" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3240,7 +3743,6 @@
           <t>https://www.apcc21.org/</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr"/>
       <c r="D117" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3249,6 +3751,11 @@
       <c r="E117" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3770,6 @@
           <t>https://www.childsupport.or.kr/</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3272,6 +3778,11 @@
       <c r="E118" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3301,6 +3812,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3313,7 +3829,6 @@
           <t>https://www.ygpa.or.kr/</t>
         </is>
       </c>
-      <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3322,6 +3837,11 @@
       <c r="E120" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3351,6 +3871,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3363,7 +3888,6 @@
           <t>https://www.kmrb.or.kr/</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3372,6 +3896,11 @@
       <c r="E122" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3915,6 @@
           <t>https://www.kofic.or.kr/</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3395,6 +3923,11 @@
       <c r="E123" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3424,6 +3957,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3451,6 +3989,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3478,6 +4021,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3505,6 +4053,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3517,7 +4070,6 @@
           <t>https://www.kicce.re.kr/</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr"/>
       <c r="D128" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3526,6 +4078,11 @@
       <c r="E128" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3540,7 +4097,6 @@
           <t>https://www.koiha.or.kr/</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr"/>
       <c r="D129" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3549,6 +4105,11 @@
       <c r="E129" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3563,7 +4124,6 @@
           <t>https://www.airport.kr/</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -3572,6 +4132,11 @@
       <c r="E130" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3586,7 +4151,6 @@
           <t>https://icpa.or.kr/</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3595,6 +4159,11 @@
       <c r="E131" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3609,7 +4178,6 @@
           <t>https://www.tacss.or.kr/</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3618,6 +4186,11 @@
       <c r="E132" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3632,7 +4205,6 @@
           <t>https://www.kicte.or.kr/</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3641,6 +4213,11 @@
       <c r="E133" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3655,7 +4232,6 @@
           <t>https://www.kcesi.or.kr/</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
       <c r="D134" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3664,6 +4240,11 @@
       <c r="E134" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3693,6 +4274,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3720,6 +4306,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3732,7 +4323,6 @@
           <t>https://www.koref.or.kr/</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
       <c r="D137" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3741,6 +4331,11 @@
       <c r="E137" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3755,7 +4350,6 @@
           <t>https://www.kdissw.or.kr/</t>
         </is>
       </c>
-      <c r="C138" t="inlineStr"/>
       <c r="D138" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3764,6 +4358,11 @@
       <c r="E138" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3793,6 +4392,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3805,7 +4409,6 @@
           <t>https://www.okocc.or.kr/</t>
         </is>
       </c>
-      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3814,6 +4417,11 @@
       <c r="E140" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3828,7 +4436,6 @@
           <t>https://hopebridge.or.kr/</t>
         </is>
       </c>
-      <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3837,6 +4444,11 @@
       <c r="E141" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3866,6 +4478,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3878,7 +4495,6 @@
           <t>https://www.jbuh.co.kr/</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr"/>
       <c r="D143" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3887,6 +4503,11 @@
       <c r="E143" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3916,6 +4537,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3928,7 +4554,6 @@
           <t>http://www.iitp.kr/</t>
         </is>
       </c>
-      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -3937,6 +4562,11 @@
       <c r="E145" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -3966,6 +4596,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3978,7 +4613,6 @@
           <t>http://www.kisdi.re.kr/</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -3987,6 +4621,11 @@
       <c r="E147" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4640,6 @@
           <t>http://www.kgls.or.kr/</t>
         </is>
       </c>
-      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4010,6 +4648,11 @@
       <c r="E148" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4667,6 @@
           <t>https://www.jdcenter.com/</t>
         </is>
       </c>
-      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -4033,6 +4675,11 @@
       <c r="E149" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4062,6 +4709,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4074,7 +4726,6 @@
           <t>https://www.srail.or.kr/</t>
         </is>
       </c>
-      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -4083,6 +4734,11 @@
       <c r="E151" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4112,6 +4768,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4124,7 +4785,6 @@
           <t>https://www.khug.or.kr/</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -4133,6 +4793,11 @@
       <c r="E153" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4162,6 +4827,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4189,6 +4859,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4201,7 +4876,6 @@
           <t>https://www.kosi.re.kr/</t>
         </is>
       </c>
-      <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4210,6 +4884,11 @@
       <c r="E156" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4903,6 @@
           <t>https://www.kosmes.or.kr/</t>
         </is>
       </c>
-      <c r="C157" t="inlineStr"/>
       <c r="D157" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -4233,6 +4911,11 @@
       <c r="E157" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4930,6 @@
           <t>https://www.kcpass.or.kr/</t>
         </is>
       </c>
-      <c r="C158" t="inlineStr"/>
       <c r="D158" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4256,6 +4938,11 @@
       <c r="E158" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4957,6 @@
           <t>https://www.kiaps.org/</t>
         </is>
       </c>
-      <c r="C159" t="inlineStr"/>
       <c r="D159" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4279,6 +4965,11 @@
       <c r="E159" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4308,6 +4999,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4335,6 +5031,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4362,6 +5063,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4389,6 +5095,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4401,7 +5112,6 @@
           <t>https://www.korailtravel.com/</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr"/>
       <c r="D164" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4410,6 +5120,11 @@
       <c r="E164" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4424,7 +5139,6 @@
           <t>https://www.korailnetworks.com/</t>
         </is>
       </c>
-      <c r="C165" t="inlineStr"/>
       <c r="D165" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4433,6 +5147,11 @@
       <c r="E165" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4462,6 +5181,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4489,6 +5213,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4501,7 +5230,6 @@
           <t>https://www.korailtech.com/</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4510,6 +5238,11 @@
       <c r="E168" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4524,7 +5257,6 @@
           <t>https://www.tpf.or.kr/</t>
         </is>
       </c>
-      <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4533,6 +5265,11 @@
       <c r="E169" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4547,7 +5284,6 @@
           <t>https://www.kinu.or.kr/</t>
         </is>
       </c>
-      <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4556,6 +5292,11 @@
       <c r="E170" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4570,7 +5311,6 @@
           <t>http://www.kopo.ac.kr/</t>
         </is>
       </c>
-      <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4579,6 +5319,11 @@
       <c r="E171" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4593,7 +5338,6 @@
           <t>https://www.kogas.or.kr/</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr"/>
       <c r="D172" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -4602,6 +5346,11 @@
       <c r="E172" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4631,6 +5380,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -4658,6 +5412,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -4685,6 +5444,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -4712,6 +5476,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -4739,6 +5508,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -4751,7 +5525,6 @@
           <t>https://keis.or.kr/</t>
         </is>
       </c>
-      <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -4760,6 +5533,11 @@
       <c r="E178" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4789,6 +5567,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -4801,7 +5584,6 @@
           <t>https://www.kcdf.or.kr/</t>
         </is>
       </c>
-      <c r="C180" t="inlineStr"/>
       <c r="D180" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4810,6 +5592,11 @@
       <c r="E180" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4824,7 +5611,6 @@
           <t>https://www.kofair.or.kr/</t>
         </is>
       </c>
-      <c r="C181" t="inlineStr"/>
       <c r="D181" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4833,6 +5619,11 @@
       <c r="E181" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4862,6 +5653,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4874,7 +5670,6 @@
           <t>https://www.kistep.re.kr/</t>
         </is>
       </c>
-      <c r="C183" t="inlineStr"/>
       <c r="D183" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4883,6 +5678,11 @@
       <c r="E183" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4897,7 +5697,6 @@
           <t>https://www.kosac.re.kr/</t>
         </is>
       </c>
-      <c r="C184" t="inlineStr"/>
       <c r="D184" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -4906,6 +5705,11 @@
       <c r="E184" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -4935,6 +5739,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4962,6 +5771,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4989,6 +5803,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5001,7 +5820,6 @@
           <t>https://www.kedi.re.kr/</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
       <c r="D188" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5010,6 +5828,11 @@
       <c r="E188" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5847,6 @@
           <t>https://www.kice.re.kr/</t>
         </is>
       </c>
-      <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5033,6 +5855,11 @@
       <c r="E189" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5047,7 +5874,6 @@
           <t>https://www.keris.or.kr/</t>
         </is>
       </c>
-      <c r="C190" t="inlineStr"/>
       <c r="D190" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5056,6 +5882,11 @@
       <c r="E190" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5070,7 +5901,6 @@
           <t>https://www.kotsa.or.kr/</t>
         </is>
       </c>
-      <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -5079,6 +5909,11 @@
       <c r="E191" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5108,6 +5943,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5120,7 +5960,6 @@
           <t>https://www.kida.re.kr/</t>
         </is>
       </c>
-      <c r="C193" t="inlineStr"/>
       <c r="D193" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5129,6 +5968,11 @@
       <c r="E193" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5158,6 +6002,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5185,6 +6034,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5197,7 +6051,6 @@
           <t>https://www.koica.go.kr/</t>
         </is>
       </c>
-      <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -5206,6 +6059,11 @@
       <c r="E196" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5220,7 +6078,6 @@
           <t>https://www.lx.or.kr/</t>
         </is>
       </c>
-      <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -5229,6 +6086,11 @@
       <c r="E197" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5258,6 +6120,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5270,7 +6137,6 @@
           <t>https://www.koreatech.ac.kr/</t>
         </is>
       </c>
-      <c r="C199" t="inlineStr"/>
       <c r="D199" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5279,6 +6145,11 @@
       <c r="E199" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5293,7 +6164,6 @@
           <t>https://www.kanc.re.kr/</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
       <c r="D200" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5302,6 +6172,11 @@
       <c r="E200" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5316,7 +6191,6 @@
           <t>https://www.koenergy.kr/</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
       <c r="D201" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -5325,6 +6199,11 @@
       <c r="E201" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5339,7 +6218,6 @@
           <t>https://www.kospo.co.kr/</t>
         </is>
       </c>
-      <c r="C202" t="inlineStr"/>
       <c r="D202" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -5348,6 +6226,11 @@
       <c r="E202" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5362,7 +6245,6 @@
           <t>https://www.kli.re.kr/</t>
         </is>
       </c>
-      <c r="C203" t="inlineStr"/>
       <c r="D203" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5371,6 +6253,11 @@
       <c r="E203" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5385,7 +6272,6 @@
           <t>https://www.kordi.or.kr/</t>
         </is>
       </c>
-      <c r="C204" t="inlineStr"/>
       <c r="D204" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5394,6 +6280,11 @@
       <c r="E204" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5423,6 +6314,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5435,7 +6331,6 @@
           <t>https://www.ekr.or.kr/</t>
         </is>
       </c>
-      <c r="C206" t="inlineStr"/>
       <c r="D206" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -5444,6 +6339,11 @@
       <c r="E206" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5473,6 +6373,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -5500,6 +6405,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -5527,6 +6437,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -5539,7 +6454,6 @@
           <t>https://www.ex.co.kr/</t>
         </is>
       </c>
-      <c r="C210" t="inlineStr"/>
       <c r="D210" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -5548,6 +6462,11 @@
       <c r="E210" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5577,6 +6496,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -5589,7 +6513,6 @@
           <t>https://www.koroad.or.kr/</t>
         </is>
       </c>
-      <c r="C212" t="inlineStr"/>
       <c r="D212" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -5598,6 +6521,11 @@
       <c r="E212" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5612,7 +6540,6 @@
           <t>https://www.kcgp.or.kr/</t>
         </is>
       </c>
-      <c r="C213" t="inlineStr"/>
       <c r="D213" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5621,6 +6548,11 @@
       <c r="E213" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5635,7 +6567,6 @@
           <t>https://www.ewp.co.kr/</t>
         </is>
       </c>
-      <c r="C214" t="inlineStr"/>
       <c r="D214" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -5644,6 +6575,11 @@
       <c r="E214" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5658,7 +6594,6 @@
           <t>https://komount.or.kr/</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr"/>
       <c r="D215" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5667,6 +6602,11 @@
       <c r="E215" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5696,6 +6636,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -5723,6 +6668,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -5735,7 +6685,6 @@
           <t>https://www.kra.co.kr/</t>
         </is>
       </c>
-      <c r="C218" t="inlineStr"/>
       <c r="D218" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -5744,6 +6693,11 @@
       <c r="E218" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5758,7 +6712,6 @@
           <t>https://drugfree.or.kr/</t>
         </is>
       </c>
-      <c r="C219" t="inlineStr"/>
       <c r="D219" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5767,6 +6720,11 @@
       <c r="E219" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5796,6 +6754,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -5823,6 +6786,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -5835,7 +6803,6 @@
           <t>http://www.kcti.re.kr/</t>
         </is>
       </c>
-      <c r="C222" t="inlineStr"/>
       <c r="D222" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5844,6 +6811,11 @@
       <c r="E222" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5873,6 +6845,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -5885,7 +6862,6 @@
           <t>https://www.arko.or.kr/</t>
         </is>
       </c>
-      <c r="C224" t="inlineStr"/>
       <c r="D224" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5894,6 +6870,11 @@
       <c r="E224" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5923,6 +6904,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -5935,7 +6921,6 @@
           <t>https://newseoulgolf.co.kr/</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr"/>
       <c r="D226" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5944,6 +6929,11 @@
       <c r="E226" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5958,7 +6948,6 @@
           <t>https://www.kwtc.or.kr/</t>
         </is>
       </c>
-      <c r="C227" t="inlineStr"/>
       <c r="D227" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -5967,6 +6956,11 @@
       <c r="E227" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -5996,6 +6990,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6023,6 +7022,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6050,6 +7054,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6062,7 +7071,6 @@
           <t>https://koreha.or.kr/</t>
         </is>
       </c>
-      <c r="C231" t="inlineStr"/>
       <c r="D231" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -6071,6 +7079,11 @@
       <c r="E231" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6100,6 +7113,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6127,6 +7145,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6139,7 +7162,6 @@
           <t>https://www.kohi.or.kr/</t>
         </is>
       </c>
-      <c r="C234" t="inlineStr"/>
       <c r="D234" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6148,6 +7170,11 @@
       <c r="E234" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6177,6 +7204,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6204,6 +7236,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6216,7 +7253,6 @@
           <t>https://www.neca.re.kr/</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6225,6 +7261,11 @@
       <c r="E237" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6239,7 +7280,6 @@
           <t>https://www.kuksiwon.or.kr/</t>
         </is>
       </c>
-      <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6248,6 +7288,11 @@
       <c r="E238" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6277,6 +7322,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6304,6 +7354,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6316,7 +7371,6 @@
           <t>https://www.kasfo.or.kr/</t>
         </is>
       </c>
-      <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6325,6 +7379,11 @@
       <c r="E241" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6339,7 +7398,6 @@
           <t>http://www.ssis.or.kr/</t>
         </is>
       </c>
-      <c r="C242" t="inlineStr"/>
       <c r="D242" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -6348,6 +7406,11 @@
       <c r="E242" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6362,7 +7425,6 @@
           <t>https://www.bokji.net/</t>
         </is>
       </c>
-      <c r="C243" t="inlineStr"/>
       <c r="D243" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6371,6 +7433,11 @@
       <c r="E243" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6385,7 +7452,6 @@
           <t>https://www.socialenterprise.or.kr/</t>
         </is>
       </c>
-      <c r="C244" t="inlineStr"/>
       <c r="D244" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6394,6 +7460,11 @@
       <c r="E244" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6408,7 +7479,6 @@
           <t>https://www.fowi.or.kr/</t>
         </is>
       </c>
-      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -6417,6 +7487,11 @@
       <c r="E245" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6446,6 +7521,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -6458,7 +7538,6 @@
           <t>https://www.ktl.re.kr/</t>
         </is>
       </c>
-      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6467,6 +7546,11 @@
       <c r="E247" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6496,6 +7580,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -6508,7 +7597,6 @@
           <t>https://www.kicox.or.kr/</t>
         </is>
       </c>
-      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -6517,6 +7605,11 @@
       <c r="E249" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6531,7 +7624,6 @@
           <t>https://kosha.or.kr/</t>
         </is>
       </c>
-      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -6540,6 +7632,11 @@
       <c r="E250" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6554,7 +7651,6 @@
           <t>http://www.kdb.co.kr/</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
       <c r="D251" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6563,6 +7659,11 @@
       <c r="E251" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6592,6 +7693,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -6604,7 +7710,6 @@
           <t>https://www.kwwa.or.kr/</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr"/>
       <c r="D253" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6613,6 +7718,11 @@
       <c r="E253" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6642,6 +7752,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -6654,7 +7769,6 @@
           <t>https://www.iwest.co.kr/</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -6663,6 +7777,11 @@
       <c r="E255" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6692,6 +7811,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -6719,6 +7843,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -6731,7 +7860,6 @@
           <t>https://www.kicet.re.kr/</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6740,6 +7868,11 @@
       <c r="E258" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6754,7 +7887,6 @@
           <t>https://www.kfi.or.kr/</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr"/>
       <c r="D259" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6763,6 +7895,11 @@
       <c r="E259" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6777,7 +7914,6 @@
           <t>https://www.kca.go.kr/</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr"/>
       <c r="D260" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -6786,6 +7922,11 @@
       <c r="E260" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6800,7 +7941,6 @@
           <t>https://www.khnp.co.kr/</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr"/>
       <c r="D261" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -6809,6 +7949,11 @@
       <c r="E261" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6838,6 +7983,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -6850,7 +8000,6 @@
           <t>http://www.fira.or.kr/</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr"/>
       <c r="D263" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6859,6 +8008,11 @@
       <c r="E263" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6888,6 +8042,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -6900,7 +8059,6 @@
           <t>https://www.kihs.re.kr/</t>
         </is>
       </c>
-      <c r="C265" t="inlineStr"/>
       <c r="D265" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6909,6 +8067,11 @@
       <c r="E265" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6923,7 +8086,6 @@
           <t>https://www.koreaexim.go.kr/</t>
         </is>
       </c>
-      <c r="C266" t="inlineStr"/>
       <c r="D266" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6932,6 +8094,11 @@
       <c r="E266" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6946,7 +8113,6 @@
           <t>https://www.kospole.co.kr/</t>
         </is>
       </c>
-      <c r="C267" t="inlineStr"/>
       <c r="D267" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -6955,6 +8121,11 @@
       <c r="E267" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -6984,6 +8155,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7011,6 +8187,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7023,7 +8204,6 @@
           <t>https://www.haccp.or.kr/</t>
         </is>
       </c>
-      <c r="C270" t="inlineStr"/>
       <c r="D270" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7032,6 +8212,11 @@
       <c r="E270" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7061,6 +8246,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7073,7 +8263,6 @@
           <t>https://www.fipa.or.kr/</t>
         </is>
       </c>
-      <c r="C272" t="inlineStr"/>
       <c r="D272" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7082,6 +8271,11 @@
       <c r="E272" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7096,7 +8290,6 @@
           <t>https://www.kpf.or.kr/</t>
         </is>
       </c>
-      <c r="C273" t="inlineStr"/>
       <c r="D273" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7105,6 +8298,11 @@
       <c r="E273" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7134,6 +8332,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7161,6 +8364,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7188,6 +8396,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7215,6 +8428,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7227,7 +8445,6 @@
           <t>https://www.stop.or.kr/</t>
         </is>
       </c>
-      <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7236,6 +8453,11 @@
       <c r="E278" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7250,7 +8472,6 @@
           <t>https://www.kwdi.re.kr/</t>
         </is>
       </c>
-      <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7259,6 +8480,11 @@
       <c r="E279" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7288,6 +8514,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7315,6 +8546,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -7327,7 +8563,6 @@
           <t>http://www.kicece.or.kr/</t>
         </is>
       </c>
-      <c r="C282" t="inlineStr"/>
       <c r="D282" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7336,6 +8571,11 @@
       <c r="E282" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7350,7 +8590,6 @@
           <t>http://www.kawf.kr/</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
       <c r="D283" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7359,6 +8598,11 @@
       <c r="E283" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7388,6 +8632,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -7415,6 +8664,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -7442,6 +8696,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -7469,6 +8728,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -7496,6 +8760,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -7508,7 +8777,6 @@
           <t>https://www.korad.or.kr/</t>
         </is>
       </c>
-      <c r="C289" t="inlineStr"/>
       <c r="D289" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7517,6 +8785,11 @@
       <c r="E289" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7531,7 +8804,6 @@
           <t>http://www.nids.or.kr/</t>
         </is>
       </c>
-      <c r="C290" t="inlineStr"/>
       <c r="D290" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7540,6 +8812,11 @@
       <c r="E290" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7554,7 +8831,6 @@
           <t>https://www.k-medi.or.kr/</t>
         </is>
       </c>
-      <c r="C291" t="inlineStr"/>
       <c r="D291" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7563,6 +8839,11 @@
       <c r="E291" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7592,6 +8873,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -7604,7 +8890,6 @@
           <t>https://www.kisa.or.kr/</t>
         </is>
       </c>
-      <c r="C293" t="inlineStr"/>
       <c r="D293" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7613,6 +8898,11 @@
       <c r="E293" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7627,7 +8917,6 @@
           <t>https://www.kofpi.or.kr/</t>
         </is>
       </c>
-      <c r="C294" t="inlineStr"/>
       <c r="D294" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7636,6 +8925,11 @@
       <c r="E294" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7650,7 +8944,6 @@
           <t>http://www.kamco.or.kr/</t>
         </is>
       </c>
-      <c r="C295" t="inlineStr"/>
       <c r="D295" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -7659,6 +8952,11 @@
       <c r="E295" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7673,7 +8971,6 @@
           <t>http://www.koreajobworld.or.kr/</t>
         </is>
       </c>
-      <c r="C296" t="inlineStr"/>
       <c r="D296" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7682,6 +8979,11 @@
       <c r="E296" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7711,6 +9013,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -7723,7 +9030,6 @@
           <t>https://www.kead.or.kr/</t>
         </is>
       </c>
-      <c r="C298" t="inlineStr"/>
       <c r="D298" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7732,6 +9038,11 @@
       <c r="E298" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7746,7 +9057,6 @@
           <t>https://www.kosaf.go.kr/</t>
         </is>
       </c>
-      <c r="C299" t="inlineStr"/>
       <c r="D299" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7755,6 +9065,11 @@
       <c r="E299" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7769,7 +9084,6 @@
           <t>https://www.fis.kr/</t>
         </is>
       </c>
-      <c r="C300" t="inlineStr"/>
       <c r="D300" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7778,6 +9092,11 @@
       <c r="E300" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7807,6 +9126,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -7819,7 +9143,6 @@
           <t>https://www.copyright.or.kr/</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
       <c r="D302" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7828,6 +9151,11 @@
       <c r="E302" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7842,7 +9170,6 @@
           <t>http://www.kesco.or.kr/</t>
         </is>
       </c>
-      <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7851,6 +9178,11 @@
       <c r="E303" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7865,7 +9197,6 @@
           <t>https://www.kpx.or.kr/</t>
         </is>
       </c>
-      <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -7874,6 +9205,11 @@
       <c r="E304" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7888,7 +9224,6 @@
           <t>https://kepco.co.kr/</t>
         </is>
       </c>
-      <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -7897,6 +9232,11 @@
       <c r="E305" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7926,6 +9266,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -7938,7 +9283,6 @@
           <t>https://www.kepco-enc.com/</t>
         </is>
       </c>
-      <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -7947,6 +9291,11 @@
       <c r="E307" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7961,7 +9310,6 @@
           <t>https://www.kips.kr/</t>
         </is>
       </c>
-      <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7970,6 +9318,11 @@
       <c r="E308" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -7984,7 +9337,6 @@
           <t>https://www.kipf.re.kr/</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -7993,6 +9345,11 @@
       <c r="E309" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8007,7 +9364,6 @@
           <t>https://www.komsco.com/</t>
         </is>
       </c>
-      <c r="C310" t="inlineStr"/>
       <c r="D310" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -8016,6 +9372,11 @@
       <c r="E310" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8030,7 +9391,6 @@
           <t>https://www.hf.go.kr/</t>
         </is>
       </c>
-      <c r="C311" t="inlineStr"/>
       <c r="D311" t="inlineStr">
         <is>
           <t>준정부기관(기금관리형)</t>
@@ -8039,6 +9399,11 @@
       <c r="E311" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8053,7 +9418,6 @@
           <t>https://www.komipo.co.kr/</t>
         </is>
       </c>
-      <c r="C312" t="inlineStr"/>
       <c r="D312" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -8062,6 +9426,11 @@
       <c r="E312" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8076,7 +9445,6 @@
           <t>https://www.kodma.or.kr/</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr"/>
       <c r="D313" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8085,6 +9453,11 @@
       <c r="E313" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8099,7 +9472,6 @@
           <t>https://www.nia.or.kr/</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr"/>
       <c r="D314" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -8108,6 +9480,11 @@
       <c r="E314" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8137,6 +9514,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -8149,7 +9531,6 @@
           <t>https://www.kiip.re.kr/</t>
         </is>
       </c>
-      <c r="C316" t="inlineStr"/>
       <c r="D316" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8158,6 +9539,11 @@
       <c r="E316" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8172,7 +9558,6 @@
           <t>https://www.kdhc.co.kr/</t>
         </is>
       </c>
-      <c r="C317" t="inlineStr"/>
       <c r="D317" t="inlineStr">
         <is>
           <t>공기업(시장형)</t>
@@ -8181,6 +9566,11 @@
       <c r="E317" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8195,7 +9585,6 @@
           <t>https://www.krivet.re.kr/</t>
         </is>
       </c>
-      <c r="C318" t="inlineStr"/>
       <c r="D318" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8204,6 +9593,11 @@
       <c r="E318" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8218,7 +9612,6 @@
           <t>https://info.korail.com/</t>
         </is>
       </c>
-      <c r="C319" t="inlineStr"/>
       <c r="D319" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -8227,6 +9620,11 @@
       <c r="E319" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8241,7 +9639,6 @@
           <t>http://www.kyci.or.kr/</t>
         </is>
       </c>
-      <c r="C320" t="inlineStr"/>
       <c r="D320" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8250,6 +9647,11 @@
       <c r="E320" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8279,6 +9681,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -8291,7 +9698,6 @@
           <t>https://www.kywa.or.kr/</t>
         </is>
       </c>
-      <c r="C322" t="inlineStr"/>
       <c r="D322" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8300,6 +9706,11 @@
       <c r="E322" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8314,7 +9725,6 @@
           <t>https://www.ksponco.or.kr/</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
       <c r="D323" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8323,6 +9733,11 @@
       <c r="E323" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8337,7 +9752,6 @@
           <t>http://www.kpipa.or.kr/</t>
         </is>
       </c>
-      <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8346,6 +9760,11 @@
       <c r="E324" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8360,7 +9779,6 @@
           <t>https://www.kafet.or.kr/</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8369,6 +9787,11 @@
       <c r="E325" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8398,6 +9821,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -8425,6 +9853,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -8452,6 +9885,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -8479,6 +9917,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -8506,6 +9949,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -8518,7 +9966,6 @@
           <t>https://www.kista.re.kr/</t>
         </is>
       </c>
-      <c r="C331" t="inlineStr"/>
       <c r="D331" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8527,6 +9974,11 @@
       <c r="E331" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8541,7 +9993,6 @@
           <t>https://www.kipi.or.kr/</t>
         </is>
       </c>
-      <c r="C332" t="inlineStr"/>
       <c r="D332" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8550,6 +10001,11 @@
       <c r="E332" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8579,6 +10035,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -8591,7 +10052,6 @@
           <t>https://www.nikom.or.kr/</t>
         </is>
       </c>
-      <c r="C334" t="inlineStr"/>
       <c r="D334" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8600,6 +10060,11 @@
       <c r="E334" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8629,6 +10094,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -8656,6 +10126,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -8668,7 +10143,6 @@
           <t>https://www.komsa.or.kr/</t>
         </is>
       </c>
-      <c r="C337" t="inlineStr"/>
       <c r="D337" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -8677,6 +10151,11 @@
       <c r="E337" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8691,7 +10170,6 @@
           <t>https://www.kmi.re.kr/</t>
         </is>
       </c>
-      <c r="C338" t="inlineStr"/>
       <c r="D338" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8700,6 +10178,11 @@
       <c r="E338" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8714,7 +10197,6 @@
           <t>https://www.seaman.or.kr/</t>
         </is>
       </c>
-      <c r="C339" t="inlineStr"/>
       <c r="D339" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8723,6 +10205,11 @@
       <c r="E339" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8737,7 +10224,6 @@
           <t>https://www.khra.kr/</t>
         </is>
       </c>
-      <c r="C340" t="inlineStr"/>
       <c r="D340" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8746,6 +10232,11 @@
       <c r="E340" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8760,7 +10251,6 @@
           <t>https://www.kobc.or.kr/</t>
         </is>
       </c>
-      <c r="C341" t="inlineStr"/>
       <c r="D341" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8769,6 +10259,11 @@
       <c r="E341" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8783,7 +10278,6 @@
           <t>https://www.kindkorea.or.kr/</t>
         </is>
       </c>
-      <c r="C342" t="inlineStr"/>
       <c r="D342" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8792,6 +10286,11 @@
       <c r="E342" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8806,7 +10305,6 @@
           <t>https://www.kipa.re.kr/</t>
         </is>
       </c>
-      <c r="C343" t="inlineStr"/>
       <c r="D343" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8815,6 +10313,11 @@
       <c r="E343" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8844,6 +10347,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -8856,7 +10364,6 @@
           <t>https://www.keco.or.kr/</t>
         </is>
       </c>
-      <c r="C345" t="inlineStr"/>
       <c r="D345" t="inlineStr">
         <is>
           <t>준정부기관(위탁집행형)</t>
@@ -8865,6 +10372,11 @@
       <c r="E345" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8879,7 +10391,6 @@
           <t>https://www.keci.or.kr/</t>
         </is>
       </c>
-      <c r="C346" t="inlineStr"/>
       <c r="D346" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8888,6 +10399,11 @@
       <c r="E346" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8917,6 +10433,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -8929,7 +10450,6 @@
           <t>https://www.kei.re.kr/</t>
         </is>
       </c>
-      <c r="C348" t="inlineStr"/>
       <c r="D348" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -8938,6 +10458,11 @@
       <c r="E348" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -8967,6 +10492,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -8994,6 +10524,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -9021,6 +10556,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -9033,7 +10573,6 @@
           <t>https://www.kepcomcs.co.kr/</t>
         </is>
       </c>
-      <c r="C352" t="inlineStr"/>
       <c r="D352" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -9042,6 +10581,11 @@
       <c r="E352" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -9071,6 +10615,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -9098,6 +10647,11 @@
           <t>기존자료 복원</t>
         </is>
       </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>SEED</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -9110,7 +10664,6 @@
           <t>https://www.kimst.re.kr/</t>
         </is>
       </c>
-      <c r="C355" t="inlineStr"/>
       <c r="D355" t="inlineStr">
         <is>
           <t>기타공공기관</t>
@@ -9119,6 +10672,11 @@
       <c r="E355" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
@@ -9133,7 +10691,6 @@
           <t>https://www.koem.or.kr/</t>
         </is>
       </c>
-      <c r="C356" t="inlineStr"/>
       <c r="D356" t="inlineStr">
         <is>
           <t>공기업(준시장형)</t>
@@ -9142,6 +10699,11 @@
       <c r="E356" t="inlineStr">
         <is>
           <t>기존자료 복원</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>DISCOVERY</t>
         </is>
       </c>
     </row>
